--- a/Data/ModelResponse/2/evaluation/2_evaluation_summary.xlsx
+++ b/Data/ModelResponse/2/evaluation/2_evaluation_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,35 +453,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy_valid_only</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Support_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>F1-Score</t>
+          <t>Predicted_as_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Precision_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Recall_0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>F1_0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Support_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Predicted_as_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Precision_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Recall_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>F1_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>actual_0_pred_0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_0_pred_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>actual_1_pred_0</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_1_pred_1</t>
         </is>
@@ -506,28 +546,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4946354166666667</v>
+        <v>0.49515625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4877358795871048</v>
+        <v>0.49515625</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4966815318806582</v>
+        <v>9554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.383464709606433</v>
+        <v>13851</v>
       </c>
       <c r="J2" t="n">
-        <v>8825</v>
+        <v>0.4949823117464443</v>
       </c>
       <c r="K2" t="n">
-        <v>729</v>
+        <v>0.7176051915428093</v>
       </c>
       <c r="L2" t="n">
-        <v>8974</v>
+        <v>0.585857722708823</v>
       </c>
       <c r="M2" t="n">
-        <v>672</v>
+        <v>9646</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4956066554496167</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2748289446402654</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3535845281760587</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6856</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2698</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6995</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2651</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +641,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy_valid_only</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Support_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>F1-Score</t>
+          <t>Predicted_as_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Precision_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Recall_0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>F1_0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Support_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Predicted_as_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Precision_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Recall_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>F1_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>actual_0_pred_0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_0_pred_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>actual_1_pred_0</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_1_pred_1</t>
         </is>
@@ -630,28 +734,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4725</v>
+        <v>0.48</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4160409413146525</v>
+        <v>0.48</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4874773980016393</v>
+        <v>387</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3422488232176814</v>
+        <v>603</v>
       </c>
       <c r="J2" t="n">
-        <v>367</v>
+        <v>0.4759535655058043</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>0.7416020671834626</v>
       </c>
       <c r="L2" t="n">
-        <v>402</v>
+        <v>0.5797979797979798</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>413</v>
+      </c>
+      <c r="N2" t="n">
+        <v>197</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4923857868020304</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2348668280871671</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3180327868852459</v>
+      </c>
+      <c r="R2" t="n">
+        <v>287</v>
+      </c>
+      <c r="S2" t="n">
+        <v>100</v>
+      </c>
+      <c r="T2" t="n">
+        <v>316</v>
+      </c>
+      <c r="U2" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -673,28 +801,52 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5075</v>
+        <v>0.51</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5188802083333333</v>
+        <v>0.51</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5029002900290029</v>
+        <v>404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.371630888966859</v>
+        <v>648</v>
       </c>
       <c r="J3" t="n">
-        <v>389</v>
+        <v>0.5092592592592593</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>0.8168316831683168</v>
       </c>
       <c r="L3" t="n">
-        <v>379</v>
+        <v>0.6273764258555132</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>396</v>
+      </c>
+      <c r="N3" t="n">
+        <v>152</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5131578947368421</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.196969696969697</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2846715328467153</v>
+      </c>
+      <c r="R3" t="n">
+        <v>330</v>
+      </c>
+      <c r="S3" t="n">
+        <v>74</v>
+      </c>
+      <c r="T3" t="n">
+        <v>318</v>
+      </c>
+      <c r="U3" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -716,28 +868,52 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.48625</v>
+        <v>0.49125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4849667458843799</v>
+        <v>0.49125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4850748719039213</v>
+        <v>821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.484545779483417</v>
+        <v>869</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>0.5040276179516686</v>
       </c>
       <c r="K4" t="n">
-        <v>386</v>
+        <v>0.5334957369062119</v>
       </c>
       <c r="L4" t="n">
-        <v>436</v>
+        <v>0.518343195266272</v>
       </c>
       <c r="M4" t="n">
-        <v>343</v>
+        <v>779</v>
+      </c>
+      <c r="N4" t="n">
+        <v>731</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4760601915184678</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4467265725288832</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4609271523178808</v>
+      </c>
+      <c r="R4" t="n">
+        <v>438</v>
+      </c>
+      <c r="S4" t="n">
+        <v>383</v>
+      </c>
+      <c r="T4" t="n">
+        <v>431</v>
+      </c>
+      <c r="U4" t="n">
+        <v>348</v>
       </c>
     </row>
     <row r="5">
@@ -759,28 +935,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.505625</v>
+        <v>0.489375</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5300156294401819</v>
+        <v>0.489375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5026407281534435</v>
+        <v>805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3571193093299482</v>
+        <v>1198</v>
       </c>
       <c r="J5" t="n">
-        <v>789</v>
+        <v>0.494991652754591</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>0.7366459627329193</v>
       </c>
       <c r="L5" t="n">
-        <v>775</v>
+        <v>0.5921118322516226</v>
       </c>
       <c r="M5" t="n">
-        <v>20</v>
+        <v>795</v>
+      </c>
+      <c r="N5" t="n">
+        <v>402</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.472636815920398</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2389937106918239</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3174603174603175</v>
+      </c>
+      <c r="R5" t="n">
+        <v>593</v>
+      </c>
+      <c r="S5" t="n">
+        <v>212</v>
+      </c>
+      <c r="T5" t="n">
+        <v>605</v>
+      </c>
+      <c r="U5" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="6">
@@ -802,28 +1002,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.509375</v>
+        <v>0.505</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4880795326045986</v>
+        <v>0.505</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4976264895029231</v>
+        <v>821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3772408297968446</v>
+        <v>1297</v>
       </c>
       <c r="J6" t="n">
-        <v>776</v>
+        <v>0.5111796453353894</v>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>0.807551766138855</v>
       </c>
       <c r="L6" t="n">
-        <v>740</v>
+        <v>0.6260623229461756</v>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>779</v>
+      </c>
+      <c r="N6" t="n">
+        <v>303</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4785478547854786</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1861360718870347</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2680221811460259</v>
+      </c>
+      <c r="R6" t="n">
+        <v>663</v>
+      </c>
+      <c r="S6" t="n">
+        <v>158</v>
+      </c>
+      <c r="T6" t="n">
+        <v>634</v>
+      </c>
+      <c r="U6" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -845,28 +1069,52 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.464375</v>
+        <v>0.4625</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5497740145317238</v>
+        <v>0.4625</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5013670647391578</v>
+        <v>740</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3240521966578246</v>
+        <v>1562</v>
       </c>
       <c r="J7" t="n">
-        <v>736</v>
+        <v>0.4615877080665813</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0.9743243243243244</v>
       </c>
       <c r="L7" t="n">
-        <v>853</v>
+        <v>0.6264118158123371</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>860</v>
+      </c>
+      <c r="N7" t="n">
+        <v>38</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.02209302325581395</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.04231625835189309</v>
+      </c>
+      <c r="R7" t="n">
+        <v>721</v>
+      </c>
+      <c r="S7" t="n">
+        <v>19</v>
+      </c>
+      <c r="T7" t="n">
+        <v>841</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -888,28 +1136,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4825</v>
+        <v>0.483125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5347998959533277</v>
+        <v>0.483125</v>
       </c>
       <c r="H8" t="n">
-        <v>0.501465481762459</v>
+        <v>769</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3357720446669234</v>
+        <v>1418</v>
       </c>
       <c r="J8" t="n">
-        <v>762</v>
+        <v>0.4795486600846262</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>0.8842652795838751</v>
       </c>
       <c r="L8" t="n">
-        <v>821</v>
+        <v>0.6218564243255601</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>831</v>
+      </c>
+      <c r="N8" t="n">
+        <v>182</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5109890109890109</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.111913357400722</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1836130306021717</v>
+      </c>
+      <c r="R8" t="n">
+        <v>680</v>
+      </c>
+      <c r="S8" t="n">
+        <v>89</v>
+      </c>
+      <c r="T8" t="n">
+        <v>738</v>
+      </c>
+      <c r="U8" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -931,28 +1203,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.511875</v>
+        <v>0.503125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.502965803923437</v>
+        <v>0.503125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5011680708535831</v>
+        <v>822</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4171573828985878</v>
+        <v>1249</v>
       </c>
       <c r="J9" t="n">
-        <v>732</v>
+        <v>0.510808646917534</v>
       </c>
       <c r="K9" t="n">
-        <v>90</v>
+        <v>0.7761557177615572</v>
       </c>
       <c r="L9" t="n">
-        <v>691</v>
+        <v>0.6161274746499277</v>
       </c>
       <c r="M9" t="n">
-        <v>87</v>
+        <v>778</v>
+      </c>
+      <c r="N9" t="n">
+        <v>351</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4757834757834758</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2146529562982005</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.295837023914969</v>
+      </c>
+      <c r="R9" t="n">
+        <v>638</v>
+      </c>
+      <c r="S9" t="n">
+        <v>184</v>
+      </c>
+      <c r="T9" t="n">
+        <v>611</v>
+      </c>
+      <c r="U9" t="n">
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -974,28 +1270,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.505</v>
+        <v>0.505625</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5574518893102964</v>
+        <v>0.505625</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5025563139078477</v>
+        <v>804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3475453659862713</v>
+        <v>1489</v>
       </c>
       <c r="J10" t="n">
-        <v>797</v>
+        <v>0.5043653458697113</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>0.9340796019900498</v>
       </c>
       <c r="L10" t="n">
-        <v>785</v>
+        <v>0.6550370693414742</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>796</v>
+      </c>
+      <c r="N10" t="n">
+        <v>111</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5225225225225225</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0728643216080402</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1278941565600882</v>
+      </c>
+      <c r="R10" t="n">
+        <v>751</v>
+      </c>
+      <c r="S10" t="n">
+        <v>53</v>
+      </c>
+      <c r="T10" t="n">
+        <v>738</v>
+      </c>
+      <c r="U10" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -1017,28 +1337,52 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.505625</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4966403928156092</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4991466830036758</v>
+        <v>812</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3873533188981848</v>
+        <v>848</v>
       </c>
       <c r="J11" t="n">
-        <v>756</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="K11" t="n">
-        <v>56</v>
+        <v>0.5320197044334976</v>
       </c>
       <c r="L11" t="n">
-        <v>735</v>
+        <v>0.5204819277108435</v>
       </c>
       <c r="M11" t="n">
-        <v>53</v>
+        <v>788</v>
+      </c>
+      <c r="N11" t="n">
+        <v>752</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4946808510638298</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.4720812182741117</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4831168831168832</v>
+      </c>
+      <c r="R11" t="n">
+        <v>432</v>
+      </c>
+      <c r="S11" t="n">
+        <v>380</v>
+      </c>
+      <c r="T11" t="n">
+        <v>416</v>
+      </c>
+      <c r="U11" t="n">
+        <v>372</v>
       </c>
     </row>
     <row r="12">
@@ -1060,28 +1404,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.49375</v>
+        <v>0.509375</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5078289319934564</v>
+        <v>0.509375</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5008376884799079</v>
+        <v>788</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3540875889126344</v>
+        <v>959</v>
       </c>
       <c r="J12" t="n">
-        <v>767</v>
+        <v>0.5015641293013556</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>0.6104060913705583</v>
       </c>
       <c r="L12" t="n">
-        <v>789</v>
+        <v>0.5506582713222667</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>812</v>
+      </c>
+      <c r="N12" t="n">
+        <v>641</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5210608424336973</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4113300492610837</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4597384721266345</v>
+      </c>
+      <c r="R12" t="n">
+        <v>481</v>
+      </c>
+      <c r="S12" t="n">
+        <v>307</v>
+      </c>
+      <c r="T12" t="n">
+        <v>478</v>
+      </c>
+      <c r="U12" t="n">
+        <v>334</v>
       </c>
     </row>
     <row r="13">
@@ -1103,28 +1471,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.510625</v>
+        <v>0.51</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5381104033970276</v>
+        <v>0.51</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5028054283084127</v>
+        <v>813</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3565191218294005</v>
+        <v>1007</v>
       </c>
       <c r="J13" t="n">
-        <v>800</v>
+        <v>0.5143992055610725</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>0.6371463714637147</v>
       </c>
       <c r="L13" t="n">
-        <v>770</v>
+        <v>0.5692307692307693</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>787</v>
+      </c>
+      <c r="N13" t="n">
+        <v>593</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5025295109612141</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3786531130876747</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4318840579710144</v>
+      </c>
+      <c r="R13" t="n">
+        <v>518</v>
+      </c>
+      <c r="S13" t="n">
+        <v>295</v>
+      </c>
+      <c r="T13" t="n">
+        <v>489</v>
+      </c>
+      <c r="U13" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="14">
@@ -1146,28 +1538,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.470625</v>
+        <v>0.485</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4418001604307805</v>
+        <v>0.485</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4885316506410256</v>
+        <v>768</v>
       </c>
       <c r="I14" t="n">
-        <v>0.351819301455202</v>
+        <v>704</v>
       </c>
       <c r="J14" t="n">
-        <v>719</v>
+        <v>0.4602272727272727</v>
       </c>
       <c r="K14" t="n">
-        <v>49</v>
+        <v>0.421875</v>
       </c>
       <c r="L14" t="n">
-        <v>798</v>
+        <v>0.4402173913043478</v>
       </c>
       <c r="M14" t="n">
-        <v>34</v>
+        <v>832</v>
+      </c>
+      <c r="N14" t="n">
+        <v>896</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5044642857142857</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.5432692307692307</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5231481481481481</v>
+      </c>
+      <c r="R14" t="n">
+        <v>324</v>
+      </c>
+      <c r="S14" t="n">
+        <v>444</v>
+      </c>
+      <c r="T14" t="n">
+        <v>380</v>
+      </c>
+      <c r="U14" t="n">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,35 +1633,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy_valid_only</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Support_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>F1-Score</t>
+          <t>Predicted_as_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Precision_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Recall_0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>F1_0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Support_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Predicted_as_1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Precision_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Recall_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>F1_1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>actual_0_pred_0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_0_pred_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>actual_1_pred_0</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_1_pred_1</t>
         </is>
@@ -1270,28 +1726,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.453125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2636865896534405</v>
+        <v>0.453125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4486745936511399</v>
+        <v>89</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3013645224171539</v>
+        <v>140</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0.6966292134831461</v>
       </c>
       <c r="L2" t="n">
-        <v>102</v>
+        <v>0.5414847161572052</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>103</v>
+      </c>
+      <c r="N2" t="n">
+        <v>52</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4807692307692308</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2427184466019418</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3225806451612904</v>
+      </c>
+      <c r="R2" t="n">
+        <v>62</v>
+      </c>
+      <c r="S2" t="n">
+        <v>27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1313,28 +1793,52 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5361111111111111</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5084718149234279</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3854073854073854</v>
+        <v>131</v>
       </c>
       <c r="J3" t="n">
-        <v>88</v>
+        <v>0.4732824427480916</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>99</v>
+      </c>
+      <c r="N3" t="n">
+        <v>61</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4918032786885246</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3749999999999999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>31</v>
+      </c>
+      <c r="T3" t="n">
+        <v>69</v>
+      </c>
+      <c r="U3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1356,28 +1860,52 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.546875</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4181315921647413</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4819290465631929</v>
+        <v>110</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3827735284336548</v>
+        <v>142</v>
       </c>
       <c r="J4" t="n">
-        <v>102</v>
+        <v>0.5774647887323944</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="L4" t="n">
-        <v>79</v>
+        <v>0.6507936507936508</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>82</v>
+      </c>
+      <c r="N4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="R4" t="n">
+        <v>82</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>60</v>
+      </c>
+      <c r="U4" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -1399,28 +1927,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.484375</v>
+        <v>0.46875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4257624398073836</v>
+        <v>0.46875</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4799240368963646</v>
+        <v>97</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3658715596330275</v>
+        <v>131</v>
       </c>
       <c r="J5" t="n">
-        <v>88</v>
+        <v>0.4809160305343512</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>0.6494845360824743</v>
       </c>
       <c r="L5" t="n">
-        <v>90</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>95</v>
+      </c>
+      <c r="N5" t="n">
+        <v>61</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2842105263157895</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="R5" t="n">
+        <v>63</v>
+      </c>
+      <c r="S5" t="n">
+        <v>34</v>
+      </c>
+      <c r="T5" t="n">
+        <v>68</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -1442,28 +1994,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4470115519839277</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4884913275880877</v>
+        <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3780281690140845</v>
+        <v>140</v>
       </c>
       <c r="J6" t="n">
-        <v>96</v>
+        <v>0.5071428571428571</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>0.6893203883495146</v>
       </c>
       <c r="L6" t="n">
-        <v>85</v>
+        <v>0.5843621399176955</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>89</v>
+      </c>
+      <c r="N6" t="n">
+        <v>52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2836879432624113</v>
+      </c>
+      <c r="R6" t="n">
+        <v>71</v>
+      </c>
+      <c r="S6" t="n">
+        <v>32</v>
+      </c>
+      <c r="T6" t="n">
+        <v>69</v>
+      </c>
+      <c r="U6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1485,28 +2061,52 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.484375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.55</v>
+        <v>0.484375</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5186712983065567</v>
+        <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4250031859309291</v>
+        <v>135</v>
       </c>
       <c r="J7" t="n">
-        <v>86</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>0.6914893617021277</v>
       </c>
       <c r="L7" t="n">
-        <v>86</v>
+        <v>0.5676855895196505</v>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
+        <v>98</v>
+      </c>
+      <c r="N7" t="n">
+        <v>57</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3612903225806451</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>70</v>
+      </c>
+      <c r="U7" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -1528,28 +2128,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.528695652173913</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>0.407563025210084</v>
+        <v>141</v>
       </c>
       <c r="J8" t="n">
-        <v>89</v>
+        <v>0.4609929078014184</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0.7065217391304348</v>
       </c>
       <c r="L8" t="n">
-        <v>91</v>
+        <v>0.5579399141630902</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>51</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3178807947019867</v>
+      </c>
+      <c r="R8" t="n">
+        <v>65</v>
+      </c>
+      <c r="S8" t="n">
+        <v>27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1571,28 +2195,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.53125</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>0.493006993006993</v>
+        <v>104</v>
       </c>
       <c r="I9" t="n">
-        <v>0.375</v>
+        <v>133</v>
       </c>
       <c r="J9" t="n">
-        <v>99</v>
+        <v>0.5488721804511278</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>0.7019230769230769</v>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>0.6160337552742616</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>88</v>
+      </c>
+      <c r="N9" t="n">
+        <v>59</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4745762711864407</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3181818181818182</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>60</v>
+      </c>
+      <c r="U9" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -1614,28 +2262,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.53125</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4801680672268908</v>
+        <v>0.53125</v>
       </c>
       <c r="H10" t="n">
-        <v>0.49352786309785</v>
+        <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4095981757247003</v>
+        <v>146</v>
       </c>
       <c r="J10" t="n">
-        <v>96</v>
+        <v>0.5547945205479452</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>0.7641509433962265</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>86</v>
+      </c>
+      <c r="N10" t="n">
+        <v>46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.2441860465116279</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3181818181818182</v>
+      </c>
+      <c r="R10" t="n">
+        <v>81</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>65</v>
+      </c>
+      <c r="U10" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1657,28 +2329,52 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>0.475891511803114</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4947916666666667</v>
+        <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3716387192550356</v>
+        <v>148</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="L11" t="n">
-        <v>91</v>
+        <v>0.6229508196721311</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>44</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="R11" t="n">
+        <v>76</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="n">
+        <v>72</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -1700,28 +2396,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4791666666666667</v>
+        <v>96</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3697478991596638</v>
+        <v>134</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>0.4477611940298508</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>0.625</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0.5217391304347827</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>96</v>
+      </c>
+      <c r="N12" t="n">
+        <v>58</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3793103448275862</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2291666666666667</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="R12" t="n">
+        <v>60</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1743,28 +2463,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.46875</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4162790697674419</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.46875</v>
+        <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3700463201235203</v>
+        <v>143</v>
       </c>
       <c r="J13" t="n">
-        <v>83</v>
+        <v>0.4755244755244755</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="L13" t="n">
-        <v>89</v>
+        <v>0.5690376569037657</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2896551724137931</v>
+      </c>
+      <c r="R13" t="n">
+        <v>68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>28</v>
+      </c>
+      <c r="T13" t="n">
+        <v>75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1786,28 +2530,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4501853568118628</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4762352160937328</v>
+        <v>109</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4171142618849041</v>
+        <v>123</v>
       </c>
       <c r="J14" t="n">
-        <v>92</v>
+        <v>0.5528455284552846</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>0.6238532110091743</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>69</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.4057971014492754</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3373493975903614</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="R14" t="n">
+        <v>68</v>
+      </c>
+      <c r="S14" t="n">
+        <v>41</v>
+      </c>
+      <c r="T14" t="n">
+        <v>55</v>
+      </c>
+      <c r="U14" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -1829,28 +2597,52 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.515625</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6277777777777778</v>
+        <v>0.515625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5299609205384281</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4139349701393497</v>
+        <v>141</v>
       </c>
       <c r="J15" t="n">
-        <v>91</v>
+        <v>0.5035460992907801</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0.7553191489361702</v>
       </c>
       <c r="L15" t="n">
-        <v>89</v>
+        <v>0.6042553191489362</v>
       </c>
       <c r="M15" t="n">
-        <v>9</v>
+        <v>98</v>
+      </c>
+      <c r="N15" t="n">
+        <v>51</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3758389261744966</v>
+      </c>
+      <c r="R15" t="n">
+        <v>71</v>
+      </c>
+      <c r="S15" t="n">
+        <v>23</v>
+      </c>
+      <c r="T15" t="n">
+        <v>70</v>
+      </c>
+      <c r="U15" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -1872,28 +2664,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5489130434782609</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5078431372549019</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>0.362972793629728</v>
+        <v>155</v>
       </c>
       <c r="J16" t="n">
-        <v>87</v>
+        <v>0.4967741935483871</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="L16" t="n">
-        <v>97</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>102</v>
+      </c>
+      <c r="N16" t="n">
+        <v>37</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.6486486486486487</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3453237410071943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>77</v>
+      </c>
+      <c r="S16" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" t="n">
+        <v>78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -1915,28 +2731,52 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5072192513368984</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5030030030030029</v>
+        <v>81</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3845969505436899</v>
+        <v>129</v>
       </c>
       <c r="J17" t="n">
+        <v>0.4418604651162791</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5428571428571429</v>
+      </c>
+      <c r="M17" t="n">
+        <v>111</v>
+      </c>
+      <c r="N17" t="n">
+        <v>63</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4482758620689656</v>
+      </c>
+      <c r="R17" t="n">
+        <v>57</v>
+      </c>
+      <c r="S17" t="n">
+        <v>24</v>
+      </c>
+      <c r="T17" t="n">
         <v>72</v>
       </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>98</v>
-      </c>
-      <c r="M17" t="n">
-        <v>13</v>
+      <c r="U17" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1958,28 +2798,52 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.546875</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4401852328273733</v>
+        <v>0.546875</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4745484400656814</v>
+        <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4011944260119442</v>
+        <v>118</v>
       </c>
       <c r="J18" t="n">
-        <v>90</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>0.6476190476190476</v>
       </c>
       <c r="L18" t="n">
-        <v>79</v>
+        <v>0.6098654708520179</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>87</v>
+      </c>
+      <c r="N18" t="n">
+        <v>74</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4252873563218391</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4596273291925466</v>
+      </c>
+      <c r="R18" t="n">
+        <v>68</v>
+      </c>
+      <c r="S18" t="n">
+        <v>37</v>
+      </c>
+      <c r="T18" t="n">
+        <v>50</v>
+      </c>
+      <c r="U18" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -2001,28 +2865,52 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.515625</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5369318181818181</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5112859468258275</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4107514107514108</v>
+        <v>137</v>
       </c>
       <c r="J19" t="n">
-        <v>90</v>
+        <v>0.4744525547445255</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>0.6701030927835051</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>95</v>
+      </c>
+      <c r="N19" t="n">
+        <v>55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4181818181818182</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2421052631578947</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="R19" t="n">
+        <v>65</v>
+      </c>
+      <c r="S19" t="n">
+        <v>32</v>
+      </c>
+      <c r="T19" t="n">
+        <v>72</v>
+      </c>
+      <c r="U19" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -2044,28 +2932,52 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>0.517032967032967</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5034265502376478</v>
+        <v>83</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3485333756143967</v>
+        <v>142</v>
       </c>
       <c r="J20" t="n">
-        <v>79</v>
+        <v>0.4788732394366197</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="L20" t="n">
-        <v>103</v>
+        <v>0.6044444444444445</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>109</v>
+      </c>
+      <c r="N20" t="n">
+        <v>50</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3211009174311927</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.440251572327044</v>
+      </c>
+      <c r="R20" t="n">
+        <v>68</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="n">
+        <v>74</v>
+      </c>
+      <c r="U20" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -2087,28 +2999,52 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4877524709926945</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4969045291625936</v>
+        <v>99</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3875390253834669</v>
+        <v>158</v>
       </c>
       <c r="J21" t="n">
-        <v>92</v>
+        <v>0.5126582278481012</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="L21" t="n">
-        <v>87</v>
+        <v>0.6303501945525292</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>93</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1720430107526882</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2519685039370079</v>
+      </c>
+      <c r="R21" t="n">
+        <v>81</v>
+      </c>
+      <c r="S21" t="n">
+        <v>18</v>
+      </c>
+      <c r="T21" t="n">
+        <v>77</v>
+      </c>
+      <c r="U21" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -2130,28 +3066,52 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4375</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5199828104856038</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5051718385051718</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3568238213399504</v>
+        <v>136</v>
       </c>
       <c r="J22" t="n">
-        <v>76</v>
+        <v>0.4264705882352941</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>0.7160493827160493</v>
       </c>
       <c r="L22" t="n">
-        <v>103</v>
+        <v>0.5345622119815668</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>111</v>
+      </c>
+      <c r="N22" t="n">
+        <v>56</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5892857142857143</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2972972972972973</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3952095808383234</v>
+      </c>
+      <c r="R22" t="n">
+        <v>58</v>
+      </c>
+      <c r="S22" t="n">
+        <v>23</v>
+      </c>
+      <c r="T22" t="n">
+        <v>78</v>
+      </c>
+      <c r="U22" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -2173,28 +3133,52 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5881226053639846</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5304232804232805</v>
+        <v>84</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4093761535622</v>
+        <v>145</v>
       </c>
       <c r="J23" t="n">
-        <v>79</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L23" t="n">
-        <v>95</v>
+        <v>0.611353711790393</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>108</v>
+      </c>
+      <c r="N23" t="n">
+        <v>47</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.4258064516129033</v>
+      </c>
+      <c r="R23" t="n">
+        <v>70</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" t="n">
+        <v>75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -2216,28 +3200,52 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4764705882352941</v>
+        <v>0.4375</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4903846153846154</v>
+        <v>88</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3857511997046881</v>
+        <v>118</v>
       </c>
       <c r="J24" t="n">
-        <v>77</v>
+        <v>0.4152542372881356</v>
       </c>
       <c r="K24" t="n">
-        <v>11</v>
+        <v>0.5568181818181818</v>
       </c>
       <c r="L24" t="n">
-        <v>93</v>
+        <v>0.4757281553398058</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>104</v>
+      </c>
+      <c r="N24" t="n">
+        <v>74</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.472972972972973</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3365384615384616</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3932584269662922</v>
+      </c>
+      <c r="R24" t="n">
+        <v>49</v>
+      </c>
+      <c r="S24" t="n">
+        <v>39</v>
+      </c>
+      <c r="T24" t="n">
+        <v>69</v>
+      </c>
+      <c r="U24" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="25">
@@ -2259,28 +3267,52 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6940266437473142</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5490387748452265</v>
+        <v>99</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4526944482150129</v>
+        <v>135</v>
       </c>
       <c r="J25" t="n">
-        <v>97</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>0.7070707070707071</v>
       </c>
       <c r="L25" t="n">
-        <v>82</v>
+        <v>0.5982905982905983</v>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>93</v>
+      </c>
+      <c r="N25" t="n">
+        <v>57</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3010752688172043</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3733333333333334</v>
+      </c>
+      <c r="R25" t="n">
+        <v>70</v>
+      </c>
+      <c r="S25" t="n">
+        <v>29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>65</v>
+      </c>
+      <c r="U25" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -2305,25 +3337,49 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4885914207484028</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4958949096880131</v>
+        <v>87</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3806451612903226</v>
+        <v>145</v>
       </c>
       <c r="J26" t="n">
-        <v>78</v>
+        <v>0.4413793103448276</v>
       </c>
       <c r="K26" t="n">
-        <v>9</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="L26" t="n">
-        <v>95</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>105</v>
+      </c>
+      <c r="N26" t="n">
+        <v>47</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.5106382978723404</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="R26" t="n">
+        <v>64</v>
+      </c>
+      <c r="S26" t="n">
+        <v>23</v>
+      </c>
+      <c r="T26" t="n">
+        <v>81</v>
+      </c>
+      <c r="U26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -2345,28 +3401,52 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6343545956805625</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H27" t="n">
-        <v>0.529104558807529</v>
+        <v>101</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4259491030454735</v>
+        <v>132</v>
       </c>
       <c r="J27" t="n">
-        <v>98</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>0.7128712871287128</v>
       </c>
       <c r="L27" t="n">
-        <v>83</v>
+        <v>0.6180257510729613</v>
       </c>
       <c r="M27" t="n">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="N27" t="n">
+        <v>60</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5166666666666667</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3406593406593407</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.4105960264900662</v>
+      </c>
+      <c r="R27" t="n">
+        <v>72</v>
+      </c>
+      <c r="S27" t="n">
+        <v>29</v>
+      </c>
+      <c r="T27" t="n">
+        <v>60</v>
+      </c>
+      <c r="U27" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -2391,25 +3471,49 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6429872495446266</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5255561584373305</v>
+        <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>0.400570109949776</v>
+        <v>145</v>
       </c>
       <c r="J28" t="n">
-        <v>93</v>
+        <v>0.5103448275862069</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="L28" t="n">
-        <v>90</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>97</v>
+      </c>
+      <c r="N28" t="n">
+        <v>47</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.2680412371134021</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="R28" t="n">
+        <v>74</v>
+      </c>
+      <c r="S28" t="n">
+        <v>21</v>
+      </c>
+      <c r="T28" t="n">
+        <v>71</v>
+      </c>
+      <c r="U28" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -2431,28 +3535,52 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5208494208494209</v>
+        <v>0.46875</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5029411764705882</v>
+        <v>90</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3530608840700584</v>
+        <v>140</v>
       </c>
       <c r="J29" t="n">
-        <v>87</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="L29" t="n">
-        <v>98</v>
+        <v>0.5565217391304348</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>102</v>
+      </c>
+      <c r="N29" t="n">
+        <v>52</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.2549019607843137</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3376623376623377</v>
+      </c>
+      <c r="R29" t="n">
+        <v>64</v>
+      </c>
+      <c r="S29" t="n">
+        <v>26</v>
+      </c>
+      <c r="T29" t="n">
+        <v>76</v>
+      </c>
+      <c r="U29" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -2474,28 +3602,52 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3158105939004815</v>
+        <v>0.4375</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4501466275659824</v>
+        <v>99</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3327710111677182</v>
+        <v>147</v>
       </c>
       <c r="J30" t="n">
-        <v>87</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="K30" t="n">
-        <v>12</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="L30" t="n">
-        <v>91</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>93</v>
+      </c>
+      <c r="N30" t="n">
+        <v>45</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="R30" t="n">
+        <v>69</v>
+      </c>
+      <c r="S30" t="n">
+        <v>30</v>
+      </c>
+      <c r="T30" t="n">
+        <v>78</v>
+      </c>
+      <c r="U30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -2517,28 +3669,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.453125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7421052631578947</v>
+        <v>0.453125</v>
       </c>
       <c r="H31" t="n">
-        <v>0.51</v>
+        <v>92</v>
       </c>
       <c r="I31" t="n">
-        <v>0.345848977889028</v>
+        <v>137</v>
       </c>
       <c r="J31" t="n">
-        <v>92</v>
+        <v>0.4525547445255474</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="L31" t="n">
-        <v>98</v>
+        <v>0.5414847161572053</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="N31" t="n">
+        <v>55</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="R31" t="n">
+        <v>62</v>
+      </c>
+      <c r="S31" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" t="n">
+        <v>75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -2560,28 +3736,52 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
+        <v>0.4427083333333333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.4427083333333333</v>
+      </c>
+      <c r="H32" t="n">
+        <v>89</v>
+      </c>
+      <c r="I32" t="n">
+        <v>144</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7078651685393258</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5407725321888412</v>
+      </c>
+      <c r="M32" t="n">
+        <v>103</v>
+      </c>
+      <c r="N32" t="n">
+        <v>48</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.4565544952285284</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.4905639794916548</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.3512670565302144</v>
-      </c>
-      <c r="J32" t="n">
-        <v>83</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>98</v>
-      </c>
-      <c r="M32" t="n">
-        <v>5</v>
+      <c r="P32" t="n">
+        <v>0.2135922330097087</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.2913907284768212</v>
+      </c>
+      <c r="R32" t="n">
+        <v>63</v>
+      </c>
+      <c r="S32" t="n">
+        <v>26</v>
+      </c>
+      <c r="T32" t="n">
+        <v>81</v>
+      </c>
+      <c r="U32" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -2603,28 +3803,52 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3092664092664092</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4731871471993053</v>
+        <v>94</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3249359959037378</v>
+        <v>154</v>
       </c>
       <c r="J33" t="n">
-        <v>88</v>
+        <v>0.487012987012987</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="L33" t="n">
-        <v>97</v>
+        <v>0.6048387096774194</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="N33" t="n">
+        <v>38</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.1938775510204082</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.2794117647058824</v>
+      </c>
+      <c r="R33" t="n">
+        <v>75</v>
+      </c>
+      <c r="S33" t="n">
+        <v>19</v>
+      </c>
+      <c r="T33" t="n">
+        <v>79</v>
+      </c>
+      <c r="U33" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -2646,28 +3870,52 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3229532898041185</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4617139133268165</v>
+        <v>93</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3247511612475116</v>
+        <v>146</v>
       </c>
       <c r="J34" t="n">
-        <v>84</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="K34" t="n">
-        <v>9</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="L34" t="n">
-        <v>97</v>
+        <v>0.602510460251046</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>99</v>
+      </c>
+      <c r="N34" t="n">
+        <v>46</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.2525252525252525</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="R34" t="n">
+        <v>72</v>
+      </c>
+      <c r="S34" t="n">
+        <v>21</v>
+      </c>
+      <c r="T34" t="n">
+        <v>74</v>
+      </c>
+      <c r="U34" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -2689,28 +3937,52 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.484375</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5182149362477231</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5032608695652174</v>
+        <v>92</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3658715596330275</v>
+        <v>147</v>
       </c>
       <c r="J35" t="n">
-        <v>88</v>
+        <v>0.4829931972789115</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>0.7717391304347826</v>
       </c>
       <c r="L35" t="n">
-        <v>95</v>
+        <v>0.5941422594142259</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="N35" t="n">
+        <v>45</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3310344827586207</v>
+      </c>
+      <c r="R35" t="n">
+        <v>71</v>
+      </c>
+      <c r="S35" t="n">
+        <v>21</v>
+      </c>
+      <c r="T35" t="n">
+        <v>76</v>
+      </c>
+      <c r="U35" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -2732,28 +4004,52 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.484375</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5967447520535443</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H36" t="n">
-        <v>0.53505291005291</v>
+        <v>84</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4176292165813904</v>
+        <v>139</v>
       </c>
       <c r="J36" t="n">
-        <v>79</v>
+        <v>0.4388489208633093</v>
       </c>
       <c r="K36" t="n">
-        <v>5</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="L36" t="n">
-        <v>94</v>
+        <v>0.547085201793722</v>
       </c>
       <c r="M36" t="n">
-        <v>14</v>
+        <v>108</v>
+      </c>
+      <c r="N36" t="n">
+        <v>53</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.5660377358490566</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.3726708074534161</v>
+      </c>
+      <c r="R36" t="n">
+        <v>61</v>
+      </c>
+      <c r="S36" t="n">
+        <v>23</v>
+      </c>
+      <c r="T36" t="n">
+        <v>78</v>
+      </c>
+      <c r="U36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -2775,28 +4071,52 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="H37" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" t="n">
+        <v>138</v>
+      </c>
+      <c r="J37" t="n">
         <v>0.5</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.4501915708812261</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.4830434782608696</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.3884538818845388</v>
-      </c>
-      <c r="J37" t="n">
-        <v>89</v>
-      </c>
       <c r="K37" t="n">
-        <v>11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>85</v>
+        <v>0.5798319327731092</v>
       </c>
       <c r="M37" t="n">
-        <v>7</v>
+        <v>92</v>
+      </c>
+      <c r="N37" t="n">
+        <v>54</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4259259259259259</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.3150684931506849</v>
+      </c>
+      <c r="R37" t="n">
+        <v>69</v>
+      </c>
+      <c r="S37" t="n">
+        <v>31</v>
+      </c>
+      <c r="T37" t="n">
+        <v>69</v>
+      </c>
+      <c r="U37" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="38">
@@ -2818,28 +4138,52 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.515625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G38" t="n">
-        <v>0.529633350075339</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5064046895353886</v>
+        <v>98</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3904761904761905</v>
+        <v>144</v>
       </c>
       <c r="J38" t="n">
-        <v>93</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>5</v>
+        <v>0.7653061224489796</v>
       </c>
       <c r="L38" t="n">
-        <v>88</v>
+        <v>0.6198347107438017</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>94</v>
+      </c>
+      <c r="N38" t="n">
+        <v>48</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.2659574468085106</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.352112676056338</v>
+      </c>
+      <c r="R38" t="n">
+        <v>75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>23</v>
+      </c>
+      <c r="T38" t="n">
+        <v>69</v>
+      </c>
+      <c r="U38" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="39">
@@ -2861,28 +4205,52 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4495798319327731</v>
+        <v>0.515625</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4834656084656085</v>
+        <v>84</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3535752895752896</v>
+        <v>131</v>
       </c>
       <c r="J39" t="n">
-        <v>75</v>
+        <v>0.4656488549618321</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0.5674418604651164</v>
       </c>
       <c r="M39" t="n">
-        <v>8</v>
+        <v>108</v>
+      </c>
+      <c r="N39" t="n">
+        <v>61</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6229508196721312</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3518518518518519</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.4497041420118343</v>
+      </c>
+      <c r="R39" t="n">
+        <v>61</v>
+      </c>
+      <c r="S39" t="n">
+        <v>23</v>
+      </c>
+      <c r="T39" t="n">
+        <v>70</v>
+      </c>
+      <c r="U39" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -2904,28 +4272,52 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G40" t="n">
-        <v>0.475095785440613</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4915327833260964</v>
+        <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3949579831932774</v>
+        <v>135</v>
       </c>
       <c r="J40" t="n">
-        <v>88</v>
+        <v>0.5037037037037037</v>
       </c>
       <c r="K40" t="n">
-        <v>10</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="L40" t="n">
-        <v>86</v>
+        <v>0.5836909871244635</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>94</v>
+      </c>
+      <c r="N40" t="n">
+        <v>57</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.2872340425531915</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.357615894039735</v>
+      </c>
+      <c r="R40" t="n">
+        <v>68</v>
+      </c>
+      <c r="S40" t="n">
+        <v>30</v>
+      </c>
+      <c r="T40" t="n">
+        <v>67</v>
+      </c>
+      <c r="U40" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -2947,28 +4339,52 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3521505376344086</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4819376026272578</v>
+        <v>105</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3543952998558918</v>
+        <v>145</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L41" t="n">
-        <v>86</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="N41" t="n">
+        <v>47</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3617021276595745</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.1954022988505747</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.2537313432835821</v>
+      </c>
+      <c r="R41" t="n">
+        <v>75</v>
+      </c>
+      <c r="S41" t="n">
+        <v>30</v>
+      </c>
+      <c r="T41" t="n">
+        <v>70</v>
+      </c>
+      <c r="U41" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -2990,28 +4406,52 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4621468926553672</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4890367622995527</v>
+        <v>89</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3638333120937938</v>
+        <v>129</v>
       </c>
       <c r="J42" t="n">
-        <v>81</v>
+        <v>0.4341085271317829</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>0.6292134831460674</v>
       </c>
       <c r="L42" t="n">
-        <v>96</v>
+        <v>0.5137614678899082</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>103</v>
+      </c>
+      <c r="N42" t="n">
+        <v>63</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.2912621359223301</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3614457831325301</v>
+      </c>
+      <c r="R42" t="n">
+        <v>56</v>
+      </c>
+      <c r="S42" t="n">
+        <v>33</v>
+      </c>
+      <c r="T42" t="n">
+        <v>73</v>
+      </c>
+      <c r="U42" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -3033,28 +4473,52 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3159415880742318</v>
+        <v>0.46875</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4343247937472862</v>
+        <v>98</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3291316983966299</v>
+        <v>130</v>
       </c>
       <c r="J43" t="n">
-        <v>82</v>
+        <v>0.4846153846153846</v>
       </c>
       <c r="K43" t="n">
-        <v>16</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L43" t="n">
-        <v>91</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>94</v>
+      </c>
+      <c r="N43" t="n">
+        <v>62</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.2872340425531915</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.3461538461538463</v>
+      </c>
+      <c r="R43" t="n">
+        <v>63</v>
+      </c>
+      <c r="S43" t="n">
+        <v>35</v>
+      </c>
+      <c r="T43" t="n">
+        <v>67</v>
+      </c>
+      <c r="U43" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -3076,28 +4540,52 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5572916666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4818007662835249</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4936603269936604</v>
+        <v>111</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4215842636895268</v>
+        <v>135</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>0.5703703703703704</v>
       </c>
       <c r="K44" t="n">
-        <v>11</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="L44" t="n">
-        <v>74</v>
+        <v>0.6260162601626017</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>81</v>
+      </c>
+      <c r="N44" t="n">
+        <v>57</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4035087719298245</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.2839506172839506</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R44" t="n">
+        <v>77</v>
+      </c>
+      <c r="S44" t="n">
+        <v>34</v>
+      </c>
+      <c r="T44" t="n">
+        <v>58</v>
+      </c>
+      <c r="U44" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -3119,28 +4607,52 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4765792866351526</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4940857297883885</v>
+        <v>95</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3757133377571334</v>
+        <v>136</v>
       </c>
       <c r="J45" t="n">
-        <v>88</v>
+        <v>0.5</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="L45" t="n">
-        <v>91</v>
+        <v>0.5887445887445888</v>
       </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>97</v>
+      </c>
+      <c r="N45" t="n">
+        <v>56</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5178571428571429</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.2989690721649484</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.3790849673202615</v>
+      </c>
+      <c r="R45" t="n">
+        <v>68</v>
+      </c>
+      <c r="S45" t="n">
+        <v>27</v>
+      </c>
+      <c r="T45" t="n">
+        <v>68</v>
+      </c>
+      <c r="U45" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -3162,28 +4674,52 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.53125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5164835164835164</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5032679738562091</v>
+        <v>102</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3915492957746479</v>
+        <v>159</v>
       </c>
       <c r="J46" t="n">
-        <v>97</v>
+        <v>0.5031446540880503</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="L46" t="n">
-        <v>85</v>
+        <v>0.6130268199233716</v>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>90</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.1222222222222222</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.1788617886178862</v>
+      </c>
+      <c r="R46" t="n">
+        <v>80</v>
+      </c>
+      <c r="S46" t="n">
+        <v>22</v>
+      </c>
+      <c r="T46" t="n">
+        <v>79</v>
+      </c>
+      <c r="U46" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="47">
@@ -3205,28 +4741,52 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.515625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5082417582417582</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5016291951775823</v>
+        <v>99</v>
       </c>
       <c r="I47" t="n">
-        <v>0.383063262274125</v>
+        <v>143</v>
       </c>
       <c r="J47" t="n">
-        <v>94</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L47" t="n">
-        <v>88</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>93</v>
+      </c>
+      <c r="N47" t="n">
+        <v>49</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.5510204081632653</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.3802816901408451</v>
+      </c>
+      <c r="R47" t="n">
+        <v>77</v>
+      </c>
+      <c r="S47" t="n">
+        <v>22</v>
+      </c>
+      <c r="T47" t="n">
+        <v>66</v>
+      </c>
+      <c r="U47" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -3251,25 +4811,49 @@
         <v>0.4947916666666667</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5300963081861958</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5081459758879113</v>
+        <v>93</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3918296705090945</v>
+        <v>150</v>
       </c>
       <c r="J48" t="n">
-        <v>87</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="L48" t="n">
-        <v>91</v>
+        <v>0.6008230452674898</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>99</v>
+      </c>
+      <c r="N48" t="n">
+        <v>42</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.3120567375886524</v>
+      </c>
+      <c r="R48" t="n">
+        <v>73</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="n">
+        <v>77</v>
+      </c>
+      <c r="U48" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -3291,28 +4875,52 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.46875</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5367425870219167</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H49" t="n">
-        <v>0.50935960591133</v>
+        <v>87</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3760672868612208</v>
+        <v>138</v>
       </c>
       <c r="J49" t="n">
-        <v>82</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="L49" t="n">
-        <v>97</v>
+        <v>0.5688888888888889</v>
       </c>
       <c r="M49" t="n">
-        <v>8</v>
+        <v>105</v>
+      </c>
+      <c r="N49" t="n">
+        <v>54</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.5740740740740741</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.2952380952380952</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.389937106918239</v>
+      </c>
+      <c r="R49" t="n">
+        <v>64</v>
+      </c>
+      <c r="S49" t="n">
+        <v>23</v>
+      </c>
+      <c r="T49" t="n">
+        <v>74</v>
+      </c>
+      <c r="U49" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="50">
@@ -3337,25 +4945,49 @@
         <v>0.46875</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5222222222222223</v>
+        <v>0.46875</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5052447552447553</v>
+        <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3700463201235203</v>
+        <v>140</v>
       </c>
       <c r="J50" t="n">
-        <v>83</v>
+        <v>0.45</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>0.7159090909090909</v>
       </c>
       <c r="L50" t="n">
-        <v>97</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>104</v>
+      </c>
+      <c r="N50" t="n">
+        <v>52</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.2596153846153846</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.3461538461538462</v>
+      </c>
+      <c r="R50" t="n">
+        <v>63</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="n">
+        <v>77</v>
+      </c>
+      <c r="U50" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -3377,28 +5009,52 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>0.513986013986014</v>
+        <v>88</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3939393939393939</v>
+        <v>150</v>
       </c>
       <c r="J51" t="n">
-        <v>82</v>
+        <v>0.5</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>0.8522727272727273</v>
       </c>
       <c r="L51" t="n">
-        <v>94</v>
+        <v>0.6302521008403361</v>
       </c>
       <c r="M51" t="n">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="N51" t="n">
+        <v>42</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.6904761904761905</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.2788461538461539</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.3972602739726028</v>
+      </c>
+      <c r="R51" t="n">
+        <v>75</v>
+      </c>
+      <c r="S51" t="n">
+        <v>13</v>
+      </c>
+      <c r="T51" t="n">
+        <v>75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="52">
@@ -3423,25 +5079,49 @@
         <v>0.4895833333333333</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5096045197740113</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5027696318018898</v>
+        <v>93</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3886939571150097</v>
+        <v>157</v>
       </c>
       <c r="J52" t="n">
-        <v>86</v>
+        <v>0.4840764331210191</v>
       </c>
       <c r="K52" t="n">
-        <v>7</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="L52" t="n">
-        <v>91</v>
+        <v>0.608</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>99</v>
+      </c>
+      <c r="N52" t="n">
+        <v>35</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="R52" t="n">
+        <v>76</v>
+      </c>
+      <c r="S52" t="n">
+        <v>17</v>
+      </c>
+      <c r="T52" t="n">
+        <v>81</v>
+      </c>
+      <c r="U52" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -3463,28 +5143,52 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4681238615664845</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4943027672273467</v>
+        <v>95</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3614768562508484</v>
+        <v>150</v>
       </c>
       <c r="J53" t="n">
-        <v>90</v>
+        <v>0.4933333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="L53" t="n">
-        <v>93</v>
+        <v>0.6040816326530611</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="N53" t="n">
+        <v>42</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.2164948453608248</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.302158273381295</v>
+      </c>
+      <c r="R53" t="n">
+        <v>74</v>
+      </c>
+      <c r="S53" t="n">
+        <v>21</v>
+      </c>
+      <c r="T53" t="n">
+        <v>76</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="54">
@@ -3506,28 +5210,52 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4529069767441861</v>
+        <v>0.515625</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4824046920821115</v>
+        <v>99</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3918296705090945</v>
+        <v>140</v>
       </c>
       <c r="J54" t="n">
-        <v>87</v>
+        <v>0.5214285714285715</v>
       </c>
       <c r="K54" t="n">
-        <v>12</v>
+        <v>0.7373737373737373</v>
       </c>
       <c r="L54" t="n">
-        <v>85</v>
+        <v>0.6108786610878661</v>
       </c>
       <c r="M54" t="n">
-        <v>8</v>
+        <v>93</v>
+      </c>
+      <c r="N54" t="n">
+        <v>52</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.2795698924731183</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.3586206896551724</v>
+      </c>
+      <c r="R54" t="n">
+        <v>73</v>
+      </c>
+      <c r="S54" t="n">
+        <v>26</v>
+      </c>
+      <c r="T54" t="n">
+        <v>67</v>
+      </c>
+      <c r="U54" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -3549,28 +5277,52 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.484375</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5372881355932203</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5107843137254902</v>
+        <v>90</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3915298184961106</v>
+        <v>138</v>
       </c>
       <c r="J55" t="n">
-        <v>84</v>
+        <v>0.463768115942029</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="L55" t="n">
-        <v>93</v>
+        <v>0.5614035087719299</v>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>102</v>
+      </c>
+      <c r="N55" t="n">
+        <v>54</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.2745098039215687</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.358974358974359</v>
+      </c>
+      <c r="R55" t="n">
+        <v>64</v>
+      </c>
+      <c r="S55" t="n">
+        <v>26</v>
+      </c>
+      <c r="T55" t="n">
+        <v>74</v>
+      </c>
+      <c r="U55" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -3592,28 +5344,52 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5201910551454625</v>
+        <v>94</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3802197802197802</v>
+        <v>147</v>
       </c>
       <c r="J56" t="n">
-        <v>93</v>
+        <v>0.4965986394557823</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="L56" t="n">
-        <v>93</v>
+        <v>0.6058091286307055</v>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>98</v>
+      </c>
+      <c r="N56" t="n">
+        <v>45</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.3356643356643357</v>
+      </c>
+      <c r="R56" t="n">
+        <v>73</v>
+      </c>
+      <c r="S56" t="n">
+        <v>21</v>
+      </c>
+      <c r="T56" t="n">
+        <v>74</v>
+      </c>
+      <c r="U56" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -3635,28 +5411,52 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.515625</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5742375601926164</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5200759631036354</v>
+        <v>95</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4107514107514108</v>
+        <v>132</v>
       </c>
       <c r="J57" t="n">
-        <v>90</v>
+        <v>0.4924242424242424</v>
       </c>
       <c r="K57" t="n">
-        <v>5</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="L57" t="n">
-        <v>88</v>
+        <v>0.5726872246696035</v>
       </c>
       <c r="M57" t="n">
-        <v>9</v>
+        <v>97</v>
+      </c>
+      <c r="N57" t="n">
+        <v>60</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.3092783505154639</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.3821656050955414</v>
+      </c>
+      <c r="R57" t="n">
+        <v>65</v>
+      </c>
+      <c r="S57" t="n">
+        <v>30</v>
+      </c>
+      <c r="T57" t="n">
+        <v>67</v>
+      </c>
+      <c r="U57" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -3678,28 +5478,52 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>0.576271186440678</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5220324230225221</v>
+        <v>91</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4071024189397839</v>
+        <v>142</v>
       </c>
       <c r="J58" t="n">
-        <v>86</v>
+        <v>0.4577464788732394</v>
       </c>
       <c r="K58" t="n">
-        <v>5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L58" t="n">
-        <v>91</v>
+        <v>0.5579399141630902</v>
       </c>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>101</v>
+      </c>
+      <c r="N58" t="n">
+        <v>50</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.2376237623762376</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.3178807947019867</v>
+      </c>
+      <c r="R58" t="n">
+        <v>65</v>
+      </c>
+      <c r="S58" t="n">
+        <v>26</v>
+      </c>
+      <c r="T58" t="n">
+        <v>77</v>
+      </c>
+      <c r="U58" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -3721,28 +5545,52 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.453125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4570262140094543</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4890734265734266</v>
+        <v>88</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3546528377989052</v>
+        <v>136</v>
       </c>
       <c r="J59" t="n">
-        <v>81</v>
+        <v>0.4558823529411765</v>
       </c>
       <c r="K59" t="n">
-        <v>7</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="L59" t="n">
-        <v>98</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>104</v>
+      </c>
+      <c r="N59" t="n">
+        <v>56</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.3749999999999999</v>
+      </c>
+      <c r="R59" t="n">
+        <v>62</v>
+      </c>
+      <c r="S59" t="n">
+        <v>26</v>
+      </c>
+      <c r="T59" t="n">
+        <v>74</v>
+      </c>
+      <c r="U59" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="60">
@@ -3764,28 +5612,52 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.578125</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5426136363636364</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5133466800133466</v>
+        <v>111</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4413592442257264</v>
+        <v>146</v>
       </c>
       <c r="J60" t="n">
-        <v>103</v>
+        <v>0.5753424657534246</v>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="L60" t="n">
-        <v>73</v>
+        <v>0.6536964980544747</v>
       </c>
       <c r="M60" t="n">
-        <v>8</v>
+        <v>81</v>
+      </c>
+      <c r="N60" t="n">
+        <v>46</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.4130434782608696</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.2992125984251969</v>
+      </c>
+      <c r="R60" t="n">
+        <v>84</v>
+      </c>
+      <c r="S60" t="n">
+        <v>27</v>
+      </c>
+      <c r="T60" t="n">
+        <v>62</v>
+      </c>
+      <c r="U60" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -3807,28 +5679,52 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.515625</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5424710424710424</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5059704732957012</v>
+        <v>98</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3752930063324353</v>
+        <v>129</v>
       </c>
       <c r="J61" t="n">
-        <v>95</v>
+        <v>0.5271317829457365</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="L61" t="n">
-        <v>90</v>
+        <v>0.5991189427312776</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>94</v>
+      </c>
+      <c r="N61" t="n">
+        <v>63</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.351063829787234</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.4203821656050956</v>
+      </c>
+      <c r="R61" t="n">
+        <v>68</v>
+      </c>
+      <c r="S61" t="n">
+        <v>30</v>
+      </c>
+      <c r="T61" t="n">
+        <v>61</v>
+      </c>
+      <c r="U61" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="62">
@@ -3850,28 +5746,52 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6436597110754414</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H62" t="n">
-        <v>0.539271610355419</v>
+        <v>106</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4591549295774647</v>
+        <v>143</v>
       </c>
       <c r="J62" t="n">
-        <v>102</v>
+        <v>0.5314685314685315</v>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>0.7169811320754716</v>
       </c>
       <c r="L62" t="n">
+        <v>0.610441767068273</v>
+      </c>
+      <c r="M62" t="n">
+        <v>86</v>
+      </c>
+      <c r="N62" t="n">
+        <v>49</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.3877551020408163</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.2209302325581395</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.2814814814814815</v>
+      </c>
+      <c r="R62" t="n">
         <v>76</v>
       </c>
-      <c r="M62" t="n">
-        <v>10</v>
+      <c r="S62" t="n">
+        <v>30</v>
+      </c>
+      <c r="T62" t="n">
+        <v>67</v>
+      </c>
+      <c r="U62" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="63">
@@ -3893,28 +5813,52 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.453125</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4954802259887006</v>
+        <v>0.453125</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4986888111888111</v>
+        <v>88</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3728872681147931</v>
+        <v>131</v>
       </c>
       <c r="J63" t="n">
-        <v>81</v>
+        <v>0.4351145038167939</v>
       </c>
       <c r="K63" t="n">
-        <v>7</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="L63" t="n">
-        <v>96</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="M63" t="n">
-        <v>8</v>
+        <v>104</v>
+      </c>
+      <c r="N63" t="n">
+        <v>61</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.4918032786885246</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="R63" t="n">
+        <v>57</v>
+      </c>
+      <c r="S63" t="n">
+        <v>31</v>
+      </c>
+      <c r="T63" t="n">
+        <v>74</v>
+      </c>
+      <c r="U63" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3936,28 +5880,52 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3828964331757628</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H64" t="n">
-        <v>0.4703514307474704</v>
+        <v>91</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3387914230019494</v>
+        <v>143</v>
       </c>
       <c r="J64" t="n">
-        <v>82</v>
+        <v>0.4685314685314685</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>0.7362637362637363</v>
       </c>
       <c r="L64" t="n">
-        <v>97</v>
+        <v>0.5726495726495727</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>101</v>
+      </c>
+      <c r="N64" t="n">
+        <v>49</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.5102040816326531</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.2475247524752475</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="R64" t="n">
+        <v>67</v>
+      </c>
+      <c r="S64" t="n">
+        <v>24</v>
+      </c>
+      <c r="T64" t="n">
+        <v>76</v>
+      </c>
+      <c r="U64" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -3979,28 +5947,52 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5178341211860764</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5045035268583831</v>
+        <v>95</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3884538818845388</v>
+        <v>140</v>
       </c>
       <c r="J65" t="n">
-        <v>89</v>
+        <v>0.4785714285714286</v>
       </c>
       <c r="K65" t="n">
-        <v>6</v>
+        <v>0.7052631578947368</v>
       </c>
       <c r="L65" t="n">
-        <v>90</v>
+        <v>0.5702127659574469</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
+        <v>97</v>
+      </c>
+      <c r="N65" t="n">
+        <v>52</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.2474226804123711</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.3221476510067114</v>
+      </c>
+      <c r="R65" t="n">
+        <v>67</v>
+      </c>
+      <c r="S65" t="n">
+        <v>28</v>
+      </c>
+      <c r="T65" t="n">
+        <v>73</v>
+      </c>
+      <c r="U65" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="66">
@@ -4022,28 +6014,52 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5112605042016807</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5037028849342323</v>
+        <v>83</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3739387227759321</v>
+        <v>136</v>
       </c>
       <c r="J66" t="n">
-        <v>76</v>
+        <v>0.4264705882352941</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>0.6987951807228916</v>
       </c>
       <c r="L66" t="n">
-        <v>99</v>
+        <v>0.5296803652968036</v>
       </c>
       <c r="M66" t="n">
-        <v>10</v>
+        <v>109</v>
+      </c>
+      <c r="N66" t="n">
+        <v>56</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.5535714285714286</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.2844036697247707</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.3757575757575757</v>
+      </c>
+      <c r="R66" t="n">
+        <v>58</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="n">
+        <v>78</v>
+      </c>
+      <c r="U66" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="67">
@@ -4065,28 +6081,52 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4681993983669961</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4919565217391304</v>
+        <v>92</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3667504816641087</v>
+        <v>144</v>
       </c>
       <c r="J67" t="n">
-        <v>85</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="K67" t="n">
-        <v>7</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="L67" t="n">
-        <v>94</v>
+        <v>0.5762711864406781</v>
       </c>
       <c r="M67" t="n">
-        <v>6</v>
+        <v>100</v>
+      </c>
+      <c r="N67" t="n">
+        <v>48</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="R67" t="n">
+        <v>68</v>
+      </c>
+      <c r="S67" t="n">
+        <v>24</v>
+      </c>
+      <c r="T67" t="n">
+        <v>76</v>
+      </c>
+      <c r="U67" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="68">
@@ -4108,28 +6148,52 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5058823529411764</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5023881893182804</v>
+        <v>98</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4194544518785382</v>
+        <v>146</v>
       </c>
       <c r="J68" t="n">
-        <v>87</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="K68" t="n">
-        <v>11</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="L68" t="n">
-        <v>83</v>
+        <v>0.5901639344262294</v>
       </c>
       <c r="M68" t="n">
-        <v>11</v>
+        <v>94</v>
+      </c>
+      <c r="N68" t="n">
+        <v>46</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.2127659574468085</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R68" t="n">
+        <v>72</v>
+      </c>
+      <c r="S68" t="n">
+        <v>26</v>
+      </c>
+      <c r="T68" t="n">
+        <v>74</v>
+      </c>
+      <c r="U68" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -4151,28 +6215,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4504107088530575</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H69" t="n">
-        <v>0.4823056882327399</v>
+        <v>94</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3792374915970421</v>
+        <v>119</v>
       </c>
       <c r="J69" t="n">
-        <v>83</v>
+        <v>0.4621848739495799</v>
       </c>
       <c r="K69" t="n">
-        <v>11</v>
+        <v>0.5851063829787234</v>
       </c>
       <c r="L69" t="n">
-        <v>90</v>
+        <v>0.5164319248826291</v>
       </c>
       <c r="M69" t="n">
-        <v>8</v>
+        <v>98</v>
+      </c>
+      <c r="N69" t="n">
+        <v>73</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.4657534246575342</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.3469387755102041</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.3976608187134503</v>
+      </c>
+      <c r="R69" t="n">
+        <v>55</v>
+      </c>
+      <c r="S69" t="n">
+        <v>39</v>
+      </c>
+      <c r="T69" t="n">
+        <v>64</v>
+      </c>
+      <c r="U69" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="70">
@@ -4194,28 +6282,52 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6192513368983957</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5123245274676689</v>
+        <v>83</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3387914230019493</v>
+        <v>152</v>
       </c>
       <c r="J70" t="n">
-        <v>82</v>
+        <v>0.4407894736842105</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="L70" t="n">
-        <v>105</v>
+        <v>0.5702127659574469</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>109</v>
+      </c>
+      <c r="N70" t="n">
+        <v>40</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.2201834862385321</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.3221476510067114</v>
+      </c>
+      <c r="R70" t="n">
+        <v>67</v>
+      </c>
+      <c r="S70" t="n">
+        <v>16</v>
+      </c>
+      <c r="T70" t="n">
+        <v>85</v>
+      </c>
+      <c r="U70" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -4237,28 +6349,52 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.46875</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4043715846994536</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4828934506353861</v>
+        <v>93</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3429951690821256</v>
+        <v>153</v>
       </c>
       <c r="J71" t="n">
-        <v>87</v>
+        <v>0.4967320261437909</v>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="L71" t="n">
-        <v>96</v>
+        <v>0.6178861788617886</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>99</v>
+      </c>
+      <c r="N71" t="n">
+        <v>39</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.3188405797101449</v>
+      </c>
+      <c r="R71" t="n">
+        <v>76</v>
+      </c>
+      <c r="S71" t="n">
+        <v>17</v>
+      </c>
+      <c r="T71" t="n">
+        <v>77</v>
+      </c>
+      <c r="U71" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -4280,28 +6416,52 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4706419227258898</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4895005984114895</v>
+        <v>101</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4011944260119442</v>
+        <v>146</v>
       </c>
       <c r="J72" t="n">
-        <v>90</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K72" t="n">
-        <v>11</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="L72" t="n">
-        <v>83</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="M72" t="n">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="N72" t="n">
+        <v>46</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.3065693430656934</v>
+      </c>
+      <c r="R72" t="n">
+        <v>76</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="n">
+        <v>70</v>
+      </c>
+      <c r="U72" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="73">
@@ -4323,28 +6483,52 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.53125</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4632574129780834</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H73" t="n">
-        <v>0.49064039408867</v>
+        <v>105</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3915492957746479</v>
+        <v>136</v>
       </c>
       <c r="J73" t="n">
-        <v>97</v>
+        <v>0.5073529411764706</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="L73" t="n">
-        <v>82</v>
+        <v>0.5726141078838175</v>
       </c>
       <c r="M73" t="n">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="N73" t="n">
+        <v>56</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.2298850574712644</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.2797202797202797</v>
+      </c>
+      <c r="R73" t="n">
+        <v>69</v>
+      </c>
+      <c r="S73" t="n">
+        <v>36</v>
+      </c>
+      <c r="T73" t="n">
+        <v>67</v>
+      </c>
+      <c r="U73" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -4366,28 +6550,52 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3615384615384615</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H74" t="n">
-        <v>0.4722222222222222</v>
+        <v>84</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3148974130240856</v>
+        <v>141</v>
       </c>
       <c r="J74" t="n">
-        <v>77</v>
+        <v>0.4397163120567376</v>
       </c>
       <c r="K74" t="n">
-        <v>7</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="L74" t="n">
-        <v>105</v>
+        <v>0.5511111111111112</v>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>108</v>
+      </c>
+      <c r="N74" t="n">
+        <v>51</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.5686274509803921</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.2685185185185185</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.3647798742138365</v>
+      </c>
+      <c r="R74" t="n">
+        <v>62</v>
+      </c>
+      <c r="S74" t="n">
+        <v>22</v>
+      </c>
+      <c r="T74" t="n">
+        <v>79</v>
+      </c>
+      <c r="U74" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="75">
@@ -4409,28 +6617,52 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4744318181818182</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4921798631476051</v>
+        <v>99</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3914929107589658</v>
+        <v>131</v>
       </c>
       <c r="J75" t="n">
-        <v>90</v>
+        <v>0.4732824427480916</v>
       </c>
       <c r="K75" t="n">
-        <v>9</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="L75" t="n">
-        <v>86</v>
+        <v>0.5391304347826086</v>
       </c>
       <c r="M75" t="n">
-        <v>7</v>
+        <v>93</v>
+      </c>
+      <c r="N75" t="n">
+        <v>61</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.3934426229508197</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.3116883116883117</v>
+      </c>
+      <c r="R75" t="n">
+        <v>62</v>
+      </c>
+      <c r="S75" t="n">
+        <v>37</v>
+      </c>
+      <c r="T75" t="n">
+        <v>69</v>
+      </c>
+      <c r="U75" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="76">
@@ -4452,28 +6684,52 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.515625</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5083333333333333</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5019550342130987</v>
+        <v>99</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3904761904761905</v>
+        <v>142</v>
       </c>
       <c r="J76" t="n">
+        <v>0.5352112676056338</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.7676767676767676</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.6307053941908715</v>
+      </c>
+      <c r="M76" t="n">
         <v>93</v>
       </c>
-      <c r="K76" t="n">
-        <v>6</v>
-      </c>
-      <c r="L76" t="n">
-        <v>87</v>
-      </c>
-      <c r="M76" t="n">
-        <v>6</v>
+      <c r="N76" t="n">
+        <v>50</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.3776223776223777</v>
+      </c>
+      <c r="R76" t="n">
+        <v>76</v>
+      </c>
+      <c r="S76" t="n">
+        <v>23</v>
+      </c>
+      <c r="T76" t="n">
+        <v>66</v>
+      </c>
+      <c r="U76" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="77">
@@ -4495,28 +6751,52 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5028409090909092</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5008681497558328</v>
+        <v>97</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3980793980793981</v>
+        <v>133</v>
       </c>
       <c r="J77" t="n">
-        <v>89</v>
+        <v>0.518796992481203</v>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>0.711340206185567</v>
       </c>
       <c r="L77" t="n">
-        <v>87</v>
+        <v>0.6</v>
       </c>
       <c r="M77" t="n">
-        <v>8</v>
+        <v>95</v>
+      </c>
+      <c r="N77" t="n">
+        <v>59</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.5254237288135594</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.3263157894736842</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.4025974025974026</v>
+      </c>
+      <c r="R77" t="n">
+        <v>69</v>
+      </c>
+      <c r="S77" t="n">
+        <v>28</v>
+      </c>
+      <c r="T77" t="n">
+        <v>64</v>
+      </c>
+      <c r="U77" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -4538,28 +6818,52 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.609375</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6448863636363636</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="H78" t="n">
-        <v>0.5453787120453787</v>
+        <v>111</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4827400409497468</v>
+        <v>143</v>
       </c>
       <c r="J78" t="n">
-        <v>106</v>
+        <v>0.6223776223776224</v>
       </c>
       <c r="K78" t="n">
-        <v>5</v>
+        <v>0.8018018018018018</v>
       </c>
       <c r="L78" t="n">
-        <v>70</v>
+        <v>0.7007874015748032</v>
       </c>
       <c r="M78" t="n">
-        <v>11</v>
+        <v>81</v>
+      </c>
+      <c r="N78" t="n">
+        <v>49</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.5510204081632653</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.4153846153846154</v>
+      </c>
+      <c r="R78" t="n">
+        <v>89</v>
+      </c>
+      <c r="S78" t="n">
+        <v>22</v>
+      </c>
+      <c r="T78" t="n">
+        <v>54</v>
+      </c>
+      <c r="U78" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="79">
@@ -4581,28 +6885,52 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.484375</v>
+        <v>0.546875</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4703666499246609</v>
+        <v>0.546875</v>
       </c>
       <c r="H79" t="n">
-        <v>0.4935953104646114</v>
+        <v>94</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3658715596330275</v>
+        <v>123</v>
       </c>
       <c r="J79" t="n">
-        <v>88</v>
+        <v>0.5284552845528455</v>
       </c>
       <c r="K79" t="n">
-        <v>6</v>
+        <v>0.6914893617021277</v>
       </c>
       <c r="L79" t="n">
-        <v>93</v>
+        <v>0.599078341013825</v>
       </c>
       <c r="M79" t="n">
-        <v>5</v>
+        <v>98</v>
+      </c>
+      <c r="N79" t="n">
+        <v>69</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.5797101449275363</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.4790419161676647</v>
+      </c>
+      <c r="R79" t="n">
+        <v>65</v>
+      </c>
+      <c r="S79" t="n">
+        <v>29</v>
+      </c>
+      <c r="T79" t="n">
+        <v>58</v>
+      </c>
+      <c r="U79" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -4624,28 +6952,52 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.46875</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5367425870219167</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H80" t="n">
-        <v>0.50935960591133</v>
+        <v>87</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3760672868612208</v>
+        <v>137</v>
       </c>
       <c r="J80" t="n">
-        <v>82</v>
+        <v>0.4379562043795621</v>
       </c>
       <c r="K80" t="n">
-        <v>5</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="L80" t="n">
-        <v>97</v>
+        <v>0.5357142857142858</v>
       </c>
       <c r="M80" t="n">
-        <v>8</v>
+        <v>105</v>
+      </c>
+      <c r="N80" t="n">
+        <v>55</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.509090909090909</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R80" t="n">
+        <v>60</v>
+      </c>
+      <c r="S80" t="n">
+        <v>27</v>
+      </c>
+      <c r="T80" t="n">
+        <v>77</v>
+      </c>
+      <c r="U80" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="81">
@@ -4667,28 +7019,52 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4446303620322483</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4802173913043478</v>
+        <v>92</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3728872681147931</v>
+        <v>138</v>
       </c>
       <c r="J81" t="n">
-        <v>81</v>
+        <v>0.5</v>
       </c>
       <c r="K81" t="n">
-        <v>11</v>
+        <v>0.75</v>
       </c>
       <c r="L81" t="n">
-        <v>92</v>
+        <v>0.6</v>
       </c>
       <c r="M81" t="n">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="N81" t="n">
+        <v>54</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.5740740740740741</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.4025974025974026</v>
+      </c>
+      <c r="R81" t="n">
+        <v>69</v>
+      </c>
+      <c r="S81" t="n">
+        <v>23</v>
+      </c>
+      <c r="T81" t="n">
+        <v>69</v>
+      </c>
+      <c r="U81" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="82">
@@ -4710,28 +7086,52 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.3802083333333333</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5197802197802197</v>
+        <v>0.3802083333333333</v>
       </c>
       <c r="H82" t="n">
-        <v>0.503968253968254</v>
+        <v>84</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3515993373263667</v>
+        <v>135</v>
       </c>
       <c r="J82" t="n">
-        <v>80</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="L82" t="n">
-        <v>102</v>
+        <v>0.45662100456621</v>
       </c>
       <c r="M82" t="n">
-        <v>6</v>
+        <v>108</v>
+      </c>
+      <c r="N82" t="n">
+        <v>57</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.4035087719298245</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.212962962962963</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.2787878787878788</v>
+      </c>
+      <c r="R82" t="n">
+        <v>50</v>
+      </c>
+      <c r="S82" t="n">
+        <v>34</v>
+      </c>
+      <c r="T82" t="n">
+        <v>85</v>
+      </c>
+      <c r="U82" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -4753,28 +7153,52 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4171122994652406</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4663482414242293</v>
+        <v>94</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3696969696969697</v>
+        <v>114</v>
       </c>
       <c r="J83" t="n">
-        <v>80</v>
+        <v>0.5</v>
       </c>
       <c r="K83" t="n">
-        <v>14</v>
+        <v>0.6063829787234043</v>
       </c>
       <c r="L83" t="n">
-        <v>90</v>
+        <v>0.5480769230769231</v>
       </c>
       <c r="M83" t="n">
-        <v>8</v>
+        <v>98</v>
+      </c>
+      <c r="N83" t="n">
+        <v>78</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.4183673469387755</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.4659090909090909</v>
+      </c>
+      <c r="R83" t="n">
+        <v>57</v>
+      </c>
+      <c r="S83" t="n">
+        <v>37</v>
+      </c>
+      <c r="T83" t="n">
+        <v>57</v>
+      </c>
+      <c r="U83" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="84">
@@ -4796,28 +7220,52 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5203488372093024</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5076360859605106</v>
+        <v>103</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4299249374478732</v>
+        <v>135</v>
       </c>
       <c r="J84" t="n">
-        <v>93</v>
+        <v>0.5851851851851851</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="L84" t="n">
+        <v>0.6638655462184874</v>
+      </c>
+      <c r="M84" t="n">
+        <v>89</v>
+      </c>
+      <c r="N84" t="n">
+        <v>57</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.3707865168539326</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.452054794520548</v>
+      </c>
+      <c r="R84" t="n">
         <v>79</v>
       </c>
-      <c r="M84" t="n">
-        <v>10</v>
+      <c r="S84" t="n">
+        <v>24</v>
+      </c>
+      <c r="T84" t="n">
+        <v>56</v>
+      </c>
+      <c r="U84" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -4839,28 +7287,52 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.515625</v>
       </c>
       <c r="G85" t="n">
-        <v>0.4184873949579831</v>
+        <v>0.515625</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4733369983507422</v>
+        <v>107</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3858990404672507</v>
+        <v>138</v>
       </c>
       <c r="J85" t="n">
-        <v>95</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>0.7102803738317757</v>
       </c>
       <c r="L85" t="n">
-        <v>80</v>
+        <v>0.6204081632653061</v>
       </c>
       <c r="M85" t="n">
-        <v>5</v>
+        <v>85</v>
+      </c>
+      <c r="N85" t="n">
+        <v>54</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.4259259259259259</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.2705882352941176</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.3309352517985611</v>
+      </c>
+      <c r="R85" t="n">
+        <v>76</v>
+      </c>
+      <c r="S85" t="n">
+        <v>31</v>
+      </c>
+      <c r="T85" t="n">
+        <v>62</v>
+      </c>
+      <c r="U85" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="86">
@@ -4882,28 +7354,52 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4706419227258898</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4895005984114895</v>
+        <v>101</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4011944260119442</v>
+        <v>146</v>
       </c>
       <c r="J86" t="n">
-        <v>90</v>
+        <v>0.5</v>
       </c>
       <c r="K86" t="n">
-        <v>11</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="L86" t="n">
-        <v>83</v>
+        <v>0.5910931174089069</v>
       </c>
       <c r="M86" t="n">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="N86" t="n">
+        <v>46</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.1978021978021978</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.2627737226277372</v>
+      </c>
+      <c r="R86" t="n">
+        <v>73</v>
+      </c>
+      <c r="S86" t="n">
+        <v>28</v>
+      </c>
+      <c r="T86" t="n">
+        <v>73</v>
+      </c>
+      <c r="U86" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -4925,28 +7421,52 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4409110442629995</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H87" t="n">
-        <v>0.4850786760716224</v>
+        <v>97</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3687600644122383</v>
+        <v>127</v>
       </c>
       <c r="J87" t="n">
-        <v>89</v>
+        <v>0.5433070866141733</v>
       </c>
       <c r="K87" t="n">
-        <v>8</v>
+        <v>0.711340206185567</v>
       </c>
       <c r="L87" t="n">
-        <v>90</v>
+        <v>0.6160714285714286</v>
       </c>
       <c r="M87" t="n">
-        <v>5</v>
+        <v>95</v>
+      </c>
+      <c r="N87" t="n">
+        <v>65</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.5692307692307692</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.3894736842105263</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="R87" t="n">
+        <v>69</v>
+      </c>
+      <c r="S87" t="n">
+        <v>28</v>
+      </c>
+      <c r="T87" t="n">
+        <v>58</v>
+      </c>
+      <c r="U87" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="88">
@@ -4971,25 +7491,49 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5626890756302521</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5202915895985203</v>
+        <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4331723027375201</v>
+        <v>123</v>
       </c>
       <c r="J88" t="n">
-        <v>94</v>
+        <v>0.5528455284552846</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>0.6732673267326733</v>
       </c>
       <c r="L88" t="n">
-        <v>81</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="M88" t="n">
-        <v>10</v>
+        <v>91</v>
+      </c>
+      <c r="N88" t="n">
+        <v>69</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.3956043956043956</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R88" t="n">
+        <v>68</v>
+      </c>
+      <c r="S88" t="n">
+        <v>33</v>
+      </c>
+      <c r="T88" t="n">
+        <v>55</v>
+      </c>
+      <c r="U88" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -5011,28 +7555,52 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.515625</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4366279069767442</v>
+        <v>0.515625</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4762190465801243</v>
+        <v>103</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3914929107589658</v>
+        <v>116</v>
       </c>
       <c r="J89" t="n">
-        <v>90</v>
+        <v>0.5431034482758621</v>
       </c>
       <c r="K89" t="n">
-        <v>13</v>
+        <v>0.6116504854368932</v>
       </c>
       <c r="L89" t="n">
-        <v>82</v>
+        <v>0.5753424657534246</v>
       </c>
       <c r="M89" t="n">
-        <v>7</v>
+        <v>89</v>
+      </c>
+      <c r="N89" t="n">
+        <v>76</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.4044943820224719</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.4363636363636363</v>
+      </c>
+      <c r="R89" t="n">
+        <v>63</v>
+      </c>
+      <c r="S89" t="n">
+        <v>40</v>
+      </c>
+      <c r="T89" t="n">
+        <v>53</v>
+      </c>
+      <c r="U89" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -5054,28 +7622,52 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.4375</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4375</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4930434782608696</v>
+        <v>100</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3945249597423511</v>
+        <v>136</v>
       </c>
       <c r="J90" t="n">
-        <v>91</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="K90" t="n">
-        <v>9</v>
+        <v>0.64</v>
       </c>
       <c r="L90" t="n">
-        <v>85</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>92</v>
+      </c>
+      <c r="N90" t="n">
+        <v>56</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.2702702702702702</v>
+      </c>
+      <c r="R90" t="n">
+        <v>64</v>
+      </c>
+      <c r="S90" t="n">
+        <v>36</v>
+      </c>
+      <c r="T90" t="n">
+        <v>72</v>
+      </c>
+      <c r="U90" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="91">
@@ -5097,28 +7689,52 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5625</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5870219166308552</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5221674876847291</v>
+        <v>105</v>
       </c>
       <c r="I91" t="n">
-        <v>0.432112676056338</v>
+        <v>125</v>
       </c>
       <c r="J91" t="n">
-        <v>100</v>
+        <v>0.592</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="L91" t="n">
-        <v>79</v>
+        <v>0.6434782608695652</v>
       </c>
       <c r="M91" t="n">
-        <v>8</v>
+        <v>87</v>
+      </c>
+      <c r="N91" t="n">
+        <v>67</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.4675324675324676</v>
+      </c>
+      <c r="R91" t="n">
+        <v>74</v>
+      </c>
+      <c r="S91" t="n">
+        <v>31</v>
+      </c>
+      <c r="T91" t="n">
+        <v>51</v>
+      </c>
+      <c r="U91" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="92">
@@ -5143,25 +7759,49 @@
         <v>0.5572916666666666</v>
       </c>
       <c r="G92" t="n">
-        <v>0.5780748663101605</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5080078982009654</v>
+        <v>106</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3879158384277838</v>
+        <v>153</v>
       </c>
       <c r="J92" t="n">
-        <v>104</v>
+        <v>0.5686274509803921</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0.8207547169811321</v>
       </c>
       <c r="L92" t="n">
-        <v>83</v>
+        <v>0.6718146718146719</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>86</v>
+      </c>
+      <c r="N92" t="n">
+        <v>39</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R92" t="n">
+        <v>87</v>
+      </c>
+      <c r="S92" t="n">
+        <v>19</v>
+      </c>
+      <c r="T92" t="n">
+        <v>66</v>
+      </c>
+      <c r="U92" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -5183,28 +7823,52 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.53125</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4989256553502364</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H93" t="n">
-        <v>0.4997272826442675</v>
+        <v>103</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3992490613266583</v>
+        <v>153</v>
       </c>
       <c r="J93" t="n">
-        <v>96</v>
+        <v>0.4967320261437909</v>
       </c>
       <c r="K93" t="n">
-        <v>7</v>
+        <v>0.7378640776699029</v>
       </c>
       <c r="L93" t="n">
-        <v>83</v>
+        <v>0.59375</v>
       </c>
       <c r="M93" t="n">
-        <v>6</v>
+        <v>89</v>
+      </c>
+      <c r="N93" t="n">
+        <v>39</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.1348314606741573</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="R93" t="n">
+        <v>76</v>
+      </c>
+      <c r="S93" t="n">
+        <v>27</v>
+      </c>
+      <c r="T93" t="n">
+        <v>77</v>
+      </c>
+      <c r="U93" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="94">
@@ -5226,28 +7890,52 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5045197740112994</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5013111888111889</v>
+        <v>104</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4095981757247003</v>
+        <v>128</v>
       </c>
       <c r="J94" t="n">
-        <v>96</v>
+        <v>0.5625</v>
       </c>
       <c r="K94" t="n">
-        <v>8</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L94" t="n">
-        <v>81</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="M94" t="n">
-        <v>7</v>
+        <v>88</v>
+      </c>
+      <c r="N94" t="n">
+        <v>64</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.4210526315789474</v>
+      </c>
+      <c r="R94" t="n">
+        <v>72</v>
+      </c>
+      <c r="S94" t="n">
+        <v>32</v>
+      </c>
+      <c r="T94" t="n">
+        <v>56</v>
+      </c>
+      <c r="U94" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="95">
@@ -5269,28 +7957,52 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4331662489557226</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4739583333333334</v>
+        <v>96</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3792374915970421</v>
+        <v>138</v>
       </c>
       <c r="J95" t="n">
-        <v>83</v>
+        <v>0.4927536231884058</v>
       </c>
       <c r="K95" t="n">
-        <v>13</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="L95" t="n">
-        <v>88</v>
+        <v>0.5811965811965812</v>
       </c>
       <c r="M95" t="n">
-        <v>8</v>
+        <v>96</v>
+      </c>
+      <c r="N95" t="n">
+        <v>54</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="R95" t="n">
+        <v>68</v>
+      </c>
+      <c r="S95" t="n">
+        <v>28</v>
+      </c>
+      <c r="T95" t="n">
+        <v>70</v>
+      </c>
+      <c r="U95" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="96">
@@ -5312,28 +8024,52 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G96" t="n">
-        <v>0.45</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4882761615284411</v>
+        <v>94</v>
       </c>
       <c r="I96" t="n">
-        <v>0.362972793629728</v>
+        <v>146</v>
       </c>
       <c r="J96" t="n">
-        <v>87</v>
+        <v>0.5</v>
       </c>
       <c r="K96" t="n">
-        <v>7</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="L96" t="n">
-        <v>93</v>
+        <v>0.6083333333333333</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>98</v>
+      </c>
+      <c r="N96" t="n">
+        <v>46</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.2551020408163265</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.3472222222222223</v>
+      </c>
+      <c r="R96" t="n">
+        <v>73</v>
+      </c>
+      <c r="S96" t="n">
+        <v>21</v>
+      </c>
+      <c r="T96" t="n">
+        <v>73</v>
+      </c>
+      <c r="U96" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -5355,28 +8091,52 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4401129943502825</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4827399044724273</v>
+        <v>94</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3667504816641087</v>
+        <v>121</v>
       </c>
       <c r="J97" t="n">
-        <v>85</v>
+        <v>0.5371900826446281</v>
       </c>
       <c r="K97" t="n">
-        <v>9</v>
+        <v>0.6914893617021277</v>
       </c>
       <c r="L97" t="n">
-        <v>92</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="M97" t="n">
-        <v>6</v>
+        <v>98</v>
+      </c>
+      <c r="N97" t="n">
+        <v>71</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.5915492957746479</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.4970414201183432</v>
+      </c>
+      <c r="R97" t="n">
+        <v>65</v>
+      </c>
+      <c r="S97" t="n">
+        <v>29</v>
+      </c>
+      <c r="T97" t="n">
+        <v>56</v>
+      </c>
+      <c r="U97" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="98">
@@ -5398,28 +8158,52 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3801031370863773</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H98" t="n">
-        <v>0.4696078431372549</v>
+        <v>90</v>
       </c>
       <c r="I98" t="n">
-        <v>0.33589785033134</v>
+        <v>135</v>
       </c>
       <c r="J98" t="n">
-        <v>81</v>
+        <v>0.4740740740740741</v>
       </c>
       <c r="K98" t="n">
-        <v>9</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="L98" t="n">
-        <v>98</v>
+        <v>0.568888888888889</v>
       </c>
       <c r="M98" t="n">
-        <v>4</v>
+        <v>102</v>
+      </c>
+      <c r="N98" t="n">
+        <v>57</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.543859649122807</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.303921568627451</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.389937106918239</v>
+      </c>
+      <c r="R98" t="n">
+        <v>64</v>
+      </c>
+      <c r="S98" t="n">
+        <v>26</v>
+      </c>
+      <c r="T98" t="n">
+        <v>71</v>
+      </c>
+      <c r="U98" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="99">
@@ -5441,28 +8225,52 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G99" t="n">
-        <v>0.496045197740113</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4988575780654989</v>
+        <v>101</v>
       </c>
       <c r="I99" t="n">
-        <v>0.400570109949776</v>
+        <v>135</v>
       </c>
       <c r="J99" t="n">
-        <v>93</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="K99" t="n">
-        <v>8</v>
+        <v>0.6534653465346535</v>
       </c>
       <c r="L99" t="n">
-        <v>84</v>
+        <v>0.5593220338983051</v>
       </c>
       <c r="M99" t="n">
-        <v>7</v>
+        <v>91</v>
+      </c>
+      <c r="N99" t="n">
+        <v>57</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.3859649122807017</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.2417582417582418</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.2972972972972973</v>
+      </c>
+      <c r="R99" t="n">
+        <v>66</v>
+      </c>
+      <c r="S99" t="n">
+        <v>35</v>
+      </c>
+      <c r="T99" t="n">
+        <v>69</v>
+      </c>
+      <c r="U99" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -5484,28 +8292,52 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.453125</v>
+        <v>0.40625</v>
       </c>
       <c r="G100" t="n">
-        <v>0.3961748633879781</v>
+        <v>0.40625</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4813725490196079</v>
+        <v>90</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3347193347193347</v>
+        <v>142</v>
       </c>
       <c r="J100" t="n">
-        <v>84</v>
+        <v>0.4154929577464789</v>
       </c>
       <c r="K100" t="n">
-        <v>6</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="L100" t="n">
-        <v>99</v>
+        <v>0.5086206896551724</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>102</v>
+      </c>
+      <c r="N100" t="n">
+        <v>50</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.1862745098039216</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R100" t="n">
+        <v>59</v>
+      </c>
+      <c r="S100" t="n">
+        <v>31</v>
+      </c>
+      <c r="T100" t="n">
+        <v>83</v>
+      </c>
+      <c r="U100" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="101">
@@ -5527,28 +8359,52 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G101" t="n">
-        <v>0.443704340352385</v>
+        <v>0.515625</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4857794181502388</v>
+        <v>98</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3716387192550357</v>
+        <v>131</v>
       </c>
       <c r="J101" t="n">
-        <v>90</v>
+        <v>0.5190839694656488</v>
       </c>
       <c r="K101" t="n">
-        <v>8</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="L101" t="n">
-        <v>89</v>
+        <v>0.5938864628820961</v>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>94</v>
+      </c>
+      <c r="N101" t="n">
+        <v>61</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.5081967213114754</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.3297872340425532</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R101" t="n">
+        <v>68</v>
+      </c>
+      <c r="S101" t="n">
+        <v>30</v>
+      </c>
+      <c r="T101" t="n">
+        <v>63</v>
+      </c>
+      <c r="U101" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -5584,10 +8440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8825</v>
+        <v>6856</v>
       </c>
       <c r="C2" t="n">
-        <v>729</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="3">
@@ -5597,10 +8453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8974</v>
+        <v>6995</v>
       </c>
       <c r="C3" t="n">
-        <v>672</v>
+        <v>2651</v>
       </c>
     </row>
   </sheetData>
@@ -5651,16 +8507,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>367</v>
+        <v>287</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>402</v>
+        <v>316</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -5670,16 +8526,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>379</v>
+        <v>318</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -5689,16 +8545,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C4" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D4" t="n">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E4" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5">
@@ -5708,16 +8564,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>789</v>
+        <v>593</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="D5" t="n">
-        <v>775</v>
+        <v>605</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
@@ -5727,16 +8583,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>776</v>
+        <v>663</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="D6" t="n">
-        <v>740</v>
+        <v>634</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -5746,16 +8602,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -5765,16 +8621,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>762</v>
+        <v>680</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="D8" t="n">
-        <v>821</v>
+        <v>738</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -5784,16 +8640,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>732</v>
+        <v>638</v>
       </c>
       <c r="C9" t="n">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="D9" t="n">
-        <v>691</v>
+        <v>611</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -5803,16 +8659,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>797</v>
+        <v>751</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
-        <v>785</v>
+        <v>738</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -5822,16 +8678,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>756</v>
+        <v>432</v>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="D11" t="n">
-        <v>735</v>
+        <v>416</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
@@ -5841,16 +8697,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>767</v>
+        <v>481</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="D12" t="n">
-        <v>789</v>
+        <v>478</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13">
@@ -5860,16 +8716,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>800</v>
+        <v>518</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="D13" t="n">
-        <v>770</v>
+        <v>489</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14">
@@ -5879,16 +8735,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>719</v>
+        <v>324</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>444</v>
       </c>
       <c r="D14" t="n">
-        <v>798</v>
+        <v>380</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ModelResponse/2/evaluation/2_evaluation_summary.xlsx
+++ b/Data/ModelResponse/2/evaluation/2_evaluation_summary.xlsx
@@ -524,40 +524,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6148958333333333</v>
+        <v>0.6396354166666667</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6148958333333333</v>
+        <v>0.6396354166666667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5722504682900722</v>
+        <v>0.598020980581802</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8953317981997069</v>
+        <v>0.8413230060707557</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6982287160231817</v>
+        <v>0.6991085018482278</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7648165569143932</v>
+        <v>0.7367598541413439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3371345635496579</v>
+        <v>0.4398714493054116</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4679810044610735</v>
+        <v>0.5508601103537812</v>
       </c>
       <c r="N2" t="n">
-        <v>8554</v>
+        <v>8038</v>
       </c>
       <c r="O2" t="n">
-        <v>1000</v>
+        <v>1516</v>
       </c>
       <c r="P2" t="n">
-        <v>6394</v>
+        <v>5403</v>
       </c>
       <c r="Q2" t="n">
-        <v>3252</v>
+        <v>4243</v>
       </c>
     </row>
   </sheetData>
@@ -680,40 +680,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.53125</v>
+        <v>0.6175</v>
       </c>
       <c r="G2" t="n">
-        <v>0.53125</v>
+        <v>0.6175</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5086705202312138</v>
+        <v>0.5635792778649922</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9095607235142119</v>
+        <v>0.9276485788113695</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6524559777571826</v>
+        <v>0.701171875</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6759259259259259</v>
+        <v>0.8282208588957055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1767554479418886</v>
+        <v>0.3268765133171913</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2802303262955855</v>
+        <v>0.46875</v>
       </c>
       <c r="N2" t="n">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="P2" t="n">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
@@ -735,40 +735,40 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5725</v>
+        <v>0.58</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5725</v>
+        <v>0.58</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5449275362318841</v>
+        <v>0.5508982035928144</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9306930693069307</v>
+        <v>0.9108910891089109</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6873857404021939</v>
+        <v>0.6865671641791045</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2070707070707071</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3241106719367589</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="N3" t="n">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="Q3" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
@@ -790,40 +790,40 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.629375</v>
+        <v>0.58125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.629375</v>
+        <v>0.58125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6628571428571428</v>
+        <v>0.6336283185840708</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5651644336175395</v>
+        <v>0.43605359317905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6101249178172256</v>
+        <v>0.5165945165945166</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6033333333333334</v>
+        <v>0.5526570048309178</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6970474967907574</v>
+        <v>0.7342747111681643</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6468135795116141</v>
+        <v>0.6306504961411246</v>
       </c>
       <c r="N4" t="n">
-        <v>464</v>
+        <v>358</v>
       </c>
       <c r="O4" t="n">
-        <v>357</v>
+        <v>463</v>
       </c>
       <c r="P4" t="n">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="Q4" t="n">
-        <v>543</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5">
@@ -845,40 +845,40 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.50125</v>
+        <v>0.516875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.50125</v>
+        <v>0.516875</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5023569023569023</v>
+        <v>0.5113154172560113</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9267080745341615</v>
+        <v>0.8981366459627329</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6515283842794759</v>
+        <v>0.6516448850833708</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4869565217391305</v>
+        <v>0.5591397849462365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07044025157232704</v>
+        <v>0.1308176100628931</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1230769230769231</v>
+        <v>0.2120285423037717</v>
       </c>
       <c r="N5" t="n">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="O5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="P5" t="n">
-        <v>739</v>
+        <v>691</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
@@ -900,40 +900,40 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5425</v>
+        <v>0.58375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5425</v>
+        <v>0.58375</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5312280701754386</v>
+        <v>0.55893536121673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9220462850182704</v>
+        <v>0.8952496954933008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.674087266251113</v>
+        <v>0.6882022471910112</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6342857142857142</v>
+        <v>0.6982456140350877</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1424903722721438</v>
+        <v>0.2554557124518614</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2327044025157233</v>
+        <v>0.3740601503759399</v>
       </c>
       <c r="N6" t="n">
-        <v>757</v>
+        <v>735</v>
       </c>
       <c r="O6" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="P6" t="n">
-        <v>668</v>
+        <v>580</v>
       </c>
       <c r="Q6" t="n">
-        <v>111</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
@@ -955,40 +955,40 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.958125</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.958125</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9232704402515723</v>
+        <v>0.8985148514851485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9918918918918919</v>
+        <v>0.9810810810810811</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9563517915309446</v>
+        <v>0.937984496124031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9925465838509316</v>
+        <v>0.9823232323232324</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9290697674418604</v>
+        <v>0.9046511627906977</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9597597597597598</v>
+        <v>0.9418886198547216</v>
       </c>
       <c r="N7" t="n">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P7" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="Q7" t="n">
-        <v>799</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -1010,40 +1010,40 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.920625</v>
+        <v>0.925</v>
       </c>
       <c r="G8" t="n">
-        <v>0.920625</v>
+        <v>0.925</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8656036446469249</v>
+        <v>0.8914354644149578</v>
       </c>
       <c r="I8" t="n">
-        <v>0.988296488946684</v>
+        <v>0.9609882964889467</v>
       </c>
       <c r="J8" t="n">
-        <v>0.922890103217972</v>
+        <v>0.9249061326658323</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9875346260387812</v>
+        <v>0.9610894941634242</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8580024067388689</v>
+        <v>0.8916967509025271</v>
       </c>
       <c r="M8" t="n">
-        <v>0.918222794591114</v>
+        <v>0.9250936329588016</v>
       </c>
       <c r="N8" t="n">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="n">
-        <v>713</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9">
@@ -1065,40 +1065,40 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.675</v>
+        <v>0.65</v>
       </c>
       <c r="G9" t="n">
-        <v>0.675</v>
+        <v>0.65</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6260434056761269</v>
+        <v>0.6100840336134454</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9124087591240876</v>
+        <v>0.8832116788321168</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7425742574257426</v>
+        <v>0.7216699801192844</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8208955223880597</v>
+        <v>0.7658536585365854</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4241645244215938</v>
+        <v>0.403598971722365</v>
       </c>
       <c r="M9" t="n">
-        <v>0.559322033898305</v>
+        <v>0.5286195286195285</v>
       </c>
       <c r="N9" t="n">
-        <v>750</v>
+        <v>726</v>
       </c>
       <c r="O9" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P9" t="n">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="Q9" t="n">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -1120,40 +1120,40 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.49875</v>
+        <v>0.594375</v>
       </c>
       <c r="G10" t="n">
-        <v>0.49875</v>
+        <v>0.594375</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5006657789613849</v>
+        <v>0.5592960979342004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9353233830845771</v>
+        <v>0.9092039800995025</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6522116218560278</v>
+        <v>0.6925627664613926</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.7508532423208191</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05778894472361809</v>
+        <v>0.2763819095477387</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1029082774049217</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="N10" t="n">
-        <v>752</v>
+        <v>731</v>
       </c>
       <c r="O10" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="P10" t="n">
-        <v>750</v>
+        <v>576</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -1175,40 +1175,40 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5131250000000001</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5131250000000001</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5123226288274833</v>
+        <v>0.5508771929824562</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6378428637842863</v>
+        <v>0.6434426229508198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1713197969543147</v>
+        <v>0.350253807106599</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2573879885605339</v>
+        <v>0.4423076923076923</v>
       </c>
       <c r="N11" t="n">
-        <v>686</v>
+        <v>628</v>
       </c>
       <c r="O11" t="n">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="P11" t="n">
-        <v>653</v>
+        <v>512</v>
       </c>
       <c r="Q11" t="n">
-        <v>135</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -1230,40 +1230,40 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.511875</v>
+        <v>0.555</v>
       </c>
       <c r="G12" t="n">
-        <v>0.511875</v>
+        <v>0.555</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5024288688410826</v>
+        <v>0.5304975922953451</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9187817258883249</v>
+        <v>0.8388324873096447</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6496186630776133</v>
+        <v>0.6499508357915438</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5974842767295597</v>
+        <v>0.6412429378531074</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1169950738916256</v>
+        <v>0.2795566502463054</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1956745623069001</v>
+        <v>0.3893653516295026</v>
       </c>
       <c r="N12" t="n">
-        <v>724</v>
+        <v>661</v>
       </c>
       <c r="O12" t="n">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="P12" t="n">
-        <v>717</v>
+        <v>585</v>
       </c>
       <c r="Q12" t="n">
-        <v>95</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
@@ -1285,40 +1285,40 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.51875</v>
+        <v>0.565625</v>
       </c>
       <c r="G13" t="n">
-        <v>0.51875</v>
+        <v>0.565625</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5140798952193845</v>
+        <v>0.5439642324888226</v>
       </c>
       <c r="I13" t="n">
-        <v>0.965559655596556</v>
+        <v>0.8979089790897909</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6709401709401709</v>
+        <v>0.6774941995359629</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6164383561643836</v>
+        <v>0.6782945736434108</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05717916137229987</v>
+        <v>0.2223634053367217</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1046511627906977</v>
+        <v>0.3349282296650717</v>
       </c>
       <c r="N13" t="n">
-        <v>785</v>
+        <v>730</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="P13" t="n">
-        <v>742</v>
+        <v>612</v>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -1340,40 +1340,40 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5575</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5575</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5235109717868338</v>
+        <v>0.5653061224489796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8697916666666666</v>
+        <v>0.7213541666666666</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6536203522504891</v>
+        <v>0.6338672768878718</v>
       </c>
       <c r="K14" t="n">
-        <v>0.691358024691358</v>
+        <v>0.6548387096774193</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.4879807692307692</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3875432525951557</v>
+        <v>0.559228650137741</v>
       </c>
       <c r="N14" t="n">
-        <v>668</v>
+        <v>554</v>
       </c>
       <c r="O14" t="n">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="P14" t="n">
-        <v>608</v>
+        <v>426</v>
       </c>
       <c r="Q14" t="n">
-        <v>224</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8554</v>
+        <v>8038</v>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="3">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6394</v>
+        <v>5403</v>
       </c>
       <c r="C3" t="n">
-        <v>3252</v>
+        <v>4243</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ModelResponse/2/evaluation/2_evaluation_summary.xlsx
+++ b/Data/ModelResponse/2/evaluation/2_evaluation_summary.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="global_metrics" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="category_metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="global_confusion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="video_metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="global_confusion" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,40 +525,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6396354166666667</v>
+        <v>0.63984375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6396354166666667</v>
+        <v>0.63984375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.598020980581802</v>
+        <v>0.5981843887193987</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8413230060707557</v>
+        <v>0.841427674272556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6991085018482278</v>
+        <v>0.6992562953942505</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7367598541413439</v>
+        <v>0.7370248220795</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4398714493054116</v>
+        <v>0.4401824590503836</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5508601103537812</v>
+        <v>0.5511780359576817</v>
       </c>
       <c r="N2" t="n">
-        <v>8038</v>
+        <v>8039</v>
       </c>
       <c r="O2" t="n">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="P2" t="n">
-        <v>5403</v>
+        <v>5400</v>
       </c>
       <c r="Q2" t="n">
-        <v>4243</v>
+        <v>4246</v>
       </c>
     </row>
   </sheetData>
@@ -680,40 +681,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6175</v>
+        <v>0.60875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6175</v>
+        <v>0.60875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5635792778649922</v>
+        <v>0.5583596214511041</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9276485788113695</v>
+        <v>0.9147286821705426</v>
       </c>
       <c r="J2" t="n">
-        <v>0.701171875</v>
+        <v>0.693437806072478</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8282208588957055</v>
+        <v>0.8012048192771084</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3268765133171913</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="M2" t="n">
-        <v>0.46875</v>
+        <v>0.4594127806563039</v>
       </c>
       <c r="N2" t="n">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="P2" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q2" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
@@ -735,40 +736,40 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58</v>
+        <v>0.58125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.58</v>
+        <v>0.58125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5508982035928144</v>
+        <v>0.5518796992481203</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9108910891089109</v>
+        <v>0.9084158415841584</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6865671641791045</v>
+        <v>0.6866230121608979</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.725925925925926</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2474747474747475</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3691148775894539</v>
       </c>
       <c r="N3" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P3" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q3" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -790,40 +791,40 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.58125</v>
+        <v>0.586875</v>
       </c>
       <c r="G4" t="n">
-        <v>0.58125</v>
+        <v>0.586875</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6336283185840708</v>
+        <v>0.6398601398601399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.43605359317905</v>
+        <v>0.4457978075517661</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5165945165945166</v>
+        <v>0.5254845656855707</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5526570048309178</v>
+        <v>0.5573929961089494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7342747111681643</v>
+        <v>0.7355584082156611</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6306504961411246</v>
+        <v>0.6342003320420586</v>
       </c>
       <c r="N4" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O4" t="n">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="P4" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q4" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5">
@@ -851,34 +852,34 @@
         <v>0.516875</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5113154172560113</v>
+        <v>0.5112994350282486</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8981366459627329</v>
+        <v>0.8993788819875776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6516448850833708</v>
+        <v>0.6519585772174696</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5591397849462365</v>
+        <v>0.5597826086956522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1308176100628931</v>
+        <v>0.129559748427673</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2120285423037717</v>
+        <v>0.2104187946884576</v>
       </c>
       <c r="N5" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P5" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Q5" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -900,28 +901,28 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.58375</v>
+        <v>0.584375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.58375</v>
+        <v>0.584375</v>
       </c>
       <c r="H6" t="n">
-        <v>0.55893536121673</v>
+        <v>0.5593607305936074</v>
       </c>
       <c r="I6" t="n">
         <v>0.8952496954933008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6882022471910112</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6982456140350877</v>
+        <v>0.6993006993006993</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2554557124518614</v>
+        <v>0.2567394094993581</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3740601503759399</v>
+        <v>0.3755868544600939</v>
       </c>
       <c r="N6" t="n">
         <v>735</v>
@@ -930,10 +931,10 @@
         <v>86</v>
       </c>
       <c r="P6" t="n">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -1010,34 +1011,34 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.925</v>
+        <v>0.925625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.925</v>
+        <v>0.925625</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8914354644149578</v>
+        <v>0.8915662650602409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9609882964889467</v>
+        <v>0.9622886866059818</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9249061326658323</v>
+        <v>0.9255784865540962</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9610894941634242</v>
+        <v>0.9623376623376624</v>
       </c>
       <c r="L8" t="n">
         <v>0.8916967509025271</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9250936329588016</v>
+        <v>0.9256714553404122</v>
       </c>
       <c r="N8" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P8" t="n">
         <v>90</v>
@@ -1065,40 +1066,40 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.65</v>
+        <v>0.658125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.65</v>
+        <v>0.658125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6100840336134454</v>
+        <v>0.6162299239222316</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8832116788321168</v>
+        <v>0.8868613138686131</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7216699801192844</v>
+        <v>0.7271820448877805</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7658536585365854</v>
+        <v>0.7769784172661871</v>
       </c>
       <c r="L9" t="n">
-        <v>0.403598971722365</v>
+        <v>0.416452442159383</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5286195286195285</v>
+        <v>0.5422594142259415</v>
       </c>
       <c r="N9" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="O9" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P9" t="n">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="Q9" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1120,40 +1121,40 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.594375</v>
+        <v>0.59375</v>
       </c>
       <c r="G10" t="n">
-        <v>0.594375</v>
+        <v>0.59375</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5592960979342004</v>
+        <v>0.5585106382978723</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9092039800995025</v>
+        <v>0.914179104477612</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6925627664613926</v>
+        <v>0.6933962264150944</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7508532423208191</v>
+        <v>0.7570422535211268</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2763819095477387</v>
+        <v>0.2701005025125628</v>
       </c>
       <c r="M10" t="n">
-        <v>0.404040404040404</v>
+        <v>0.3981481481481482</v>
       </c>
       <c r="N10" t="n">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="O10" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P10" t="n">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="Q10" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -1175,40 +1176,40 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5525</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5525</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5508771929824562</v>
+        <v>0.5424028268551236</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.7561576354679803</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6434426229508198</v>
+        <v>0.6316872427983539</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="L11" t="n">
-        <v>0.350253807106599</v>
+        <v>0.3426395939086294</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4423076923076923</v>
+        <v>0.429936305732484</v>
       </c>
       <c r="N11" t="n">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="O11" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="P11" t="n">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="Q11" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
@@ -1230,40 +1231,40 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.555</v>
+        <v>0.55125</v>
       </c>
       <c r="G12" t="n">
-        <v>0.555</v>
+        <v>0.55125</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5304975922953451</v>
+        <v>0.5281350482315113</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8388324873096447</v>
+        <v>0.8337563451776649</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6499508357915438</v>
+        <v>0.6466535433070866</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6412429378531074</v>
+        <v>0.6320224719101124</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2795566502463054</v>
+        <v>0.2770935960591133</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3893653516295026</v>
+        <v>0.3852739726027398</v>
       </c>
       <c r="N12" t="n">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="O12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="P12" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="Q12" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
@@ -1285,34 +1286,34 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.565625</v>
+        <v>0.569375</v>
       </c>
       <c r="G13" t="n">
-        <v>0.565625</v>
+        <v>0.569375</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5439642324888226</v>
+        <v>0.5459940652818991</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8979089790897909</v>
+        <v>0.9052890528905289</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6774941995359629</v>
+        <v>0.6811661267931512</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6782945736434108</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="L13" t="n">
         <v>0.2223634053367217</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3349282296650717</v>
+        <v>0.3368623676612127</v>
       </c>
       <c r="N13" t="n">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="O13" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="P13" t="n">
         <v>612</v>
@@ -1340,40 +1341,40 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.604375</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>0.604375</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5653061224489796</v>
+        <v>0.5690890481064483</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7213541666666666</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6338672768878718</v>
+        <v>0.6372492836676218</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6548387096774193</v>
+        <v>0.6597110754414125</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4879807692307692</v>
+        <v>0.4939903846153846</v>
       </c>
       <c r="M14" t="n">
-        <v>0.559228650137741</v>
+        <v>0.5649484536082474</v>
       </c>
       <c r="N14" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O14" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P14" t="n">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="Q14" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -1387,6 +1388,5607 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>video_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>total_examples</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>valid_answers</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>invalid_answers</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>empty_answers</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>overall_accuracy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>valid_only_accuracy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>precision_label_0</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>recall_label_0</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>f1_label_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>precision_label_1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>recall_label_1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>f1_label_1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>true_0_pred_0</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>true_0_pred_1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>true_1_pred_0</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>true_1_pred_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Video1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>192</v>
+      </c>
+      <c r="C2" t="n">
+        <v>192</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6101694915254238</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8089887640449438</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6956521739130436</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7702702702702703</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5533980582524272</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6440677966101694</v>
+      </c>
+      <c r="N2" t="n">
+        <v>72</v>
+      </c>
+      <c r="O2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Video2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>192</v>
+      </c>
+      <c r="C3" t="n">
+        <v>192</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5612903225806452</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7016129032258064</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3131313131313131</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4558823529411765</v>
+      </c>
+      <c r="N3" t="n">
+        <v>87</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Video3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>192</v>
+      </c>
+      <c r="C4" t="n">
+        <v>192</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7384615384615385</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4516129032258065</v>
+      </c>
+      <c r="N4" t="n">
+        <v>96</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Video4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>192</v>
+      </c>
+      <c r="C5" t="n">
+        <v>192</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5845070422535211</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8556701030927835</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6945606694560669</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3789473684210526</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.496551724137931</v>
+      </c>
+      <c r="N5" t="n">
+        <v>83</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Video5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>192</v>
+      </c>
+      <c r="C6" t="n">
+        <v>192</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5974842767295597</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9223300970873787</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7251908396946564</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2808988764044944</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4098360655737705</v>
+      </c>
+      <c r="N6" t="n">
+        <v>95</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Video6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>192</v>
+      </c>
+      <c r="C7" t="n">
+        <v>192</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6090225563909775</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8617021276595744</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7136563876651983</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7796610169491526</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4693877551020408</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5859872611464969</v>
+      </c>
+      <c r="N7" t="n">
+        <v>81</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Video7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>192</v>
+      </c>
+      <c r="C8" t="n">
+        <v>192</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6349206349206349</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7339449541284404</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.6506024096385542</v>
+      </c>
+      <c r="N8" t="n">
+        <v>80</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Video8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>192</v>
+      </c>
+      <c r="C9" t="n">
+        <v>192</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6418918918918919</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9134615384615384</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7539682539682538</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3977272727272727</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="N9" t="n">
+        <v>95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Video9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>192</v>
+      </c>
+      <c r="C10" t="n">
+        <v>192</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6164383561643836</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7142857142857144</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="N10" t="n">
+        <v>90</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Video10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>192</v>
+      </c>
+      <c r="C11" t="n">
+        <v>192</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7070707070707071</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6881720430107527</v>
+      </c>
+      <c r="N11" t="n">
+        <v>70</v>
+      </c>
+      <c r="O11" t="n">
+        <v>26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Video11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>192</v>
+      </c>
+      <c r="C12" t="n">
+        <v>192</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6126126126126126</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6570048309178743</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.654320987654321</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5988700564971753</v>
+      </c>
+      <c r="N12" t="n">
+        <v>68</v>
+      </c>
+      <c r="O12" t="n">
+        <v>28</v>
+      </c>
+      <c r="P12" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Video12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>192</v>
+      </c>
+      <c r="C13" t="n">
+        <v>192</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5677083333333334</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5677083333333334</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5496183206106871</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6343612334801763</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6065573770491803</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3854166666666667</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4713375796178344</v>
+      </c>
+      <c r="N13" t="n">
+        <v>72</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Video13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>192</v>
+      </c>
+      <c r="C14" t="n">
+        <v>192</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6747967479674797</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7614678899082569</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7155172413793104</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6231884057971014</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5180722891566265</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5657894736842106</v>
+      </c>
+      <c r="N14" t="n">
+        <v>83</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Video14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>192</v>
+      </c>
+      <c r="C15" t="n">
+        <v>192</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5859375</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7978723404255319</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4591836734693878</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="N15" t="n">
+        <v>75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>19</v>
+      </c>
+      <c r="P15" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Video15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>192</v>
+      </c>
+      <c r="C16" t="n">
+        <v>192</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5592105263157895</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7024793388429752</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3431372549019608</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4929577464788732</v>
+      </c>
+      <c r="N16" t="n">
+        <v>85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Video16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>192</v>
+      </c>
+      <c r="C17" t="n">
+        <v>192</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4788732394366197</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8395061728395061</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6098654708520179</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4596273291925466</v>
+      </c>
+      <c r="N17" t="n">
+        <v>68</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Video17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>192</v>
+      </c>
+      <c r="C18" t="n">
+        <v>192</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6283185840707964</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6761904761904762</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6513761467889908</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.569620253164557</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5421686746987951</v>
+      </c>
+      <c r="N18" t="n">
+        <v>71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Video18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>192</v>
+      </c>
+      <c r="C19" t="n">
+        <v>192</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6804123711340206</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6804123711340206</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6804123711340206</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.6736842105263158</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6736842105263158</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6736842105263158</v>
+      </c>
+      <c r="N19" t="n">
+        <v>66</v>
+      </c>
+      <c r="O19" t="n">
+        <v>31</v>
+      </c>
+      <c r="P19" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Video19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>192</v>
+      </c>
+      <c r="C20" t="n">
+        <v>192</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5989583333333334</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5989583333333334</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9397590361445783</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.6695278969957081</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3394495412844037</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4900662251655629</v>
+      </c>
+      <c r="N20" t="n">
+        <v>78</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Video20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>192</v>
+      </c>
+      <c r="C21" t="n">
+        <v>192</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9494949494949495</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.725868725868726</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="N21" t="n">
+        <v>94</v>
+      </c>
+      <c r="O21" t="n">
+        <v>5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Video21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>192</v>
+      </c>
+      <c r="C22" t="n">
+        <v>192</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.647887323943662</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4324324324324325</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5614035087719298</v>
+      </c>
+      <c r="N22" t="n">
+        <v>69</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Video22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>192</v>
+      </c>
+      <c r="C23" t="n">
+        <v>192</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5673758865248227</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9215686274509803</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.4351851851851852</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.5911949685534591</v>
+      </c>
+      <c r="N23" t="n">
+        <v>80</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Video23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>192</v>
+      </c>
+      <c r="C24" t="n">
+        <v>192</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5251798561151079</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8295454545454546</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6431718061674009</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7169811320754716</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.3653846153846154</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4840764331210192</v>
+      </c>
+      <c r="N24" t="n">
+        <v>73</v>
+      </c>
+      <c r="O24" t="n">
+        <v>15</v>
+      </c>
+      <c r="P24" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Video24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>192</v>
+      </c>
+      <c r="C25" t="n">
+        <v>192</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7227722772277227</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7373737373737373</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7300000000000001</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6989247311827957</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.7065217391304348</v>
+      </c>
+      <c r="N25" t="n">
+        <v>73</v>
+      </c>
+      <c r="O25" t="n">
+        <v>26</v>
+      </c>
+      <c r="P25" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Video25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>192</v>
+      </c>
+      <c r="C26" t="n">
+        <v>192</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5671641791044776</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8735632183908046</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6877828054298641</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8103448275862069</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.4476190476190476</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5766871165644172</v>
+      </c>
+      <c r="N26" t="n">
+        <v>76</v>
+      </c>
+      <c r="O26" t="n">
+        <v>11</v>
+      </c>
+      <c r="P26" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Video26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>192</v>
+      </c>
+      <c r="C27" t="n">
+        <v>192</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.801980198019802</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7864077669902912</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.7701149425287356</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.7362637362637363</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.752808988764045</v>
+      </c>
+      <c r="N27" t="n">
+        <v>81</v>
+      </c>
+      <c r="O27" t="n">
+        <v>20</v>
+      </c>
+      <c r="P27" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Video27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>192</v>
+      </c>
+      <c r="C28" t="n">
+        <v>192</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7184466019417476</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7789473684210526</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7474747474747476</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.7640449438202247</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7010309278350515</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.7311827956989247</v>
+      </c>
+      <c r="N28" t="n">
+        <v>74</v>
+      </c>
+      <c r="O28" t="n">
+        <v>21</v>
+      </c>
+      <c r="P28" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Video28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>192</v>
+      </c>
+      <c r="C29" t="n">
+        <v>192</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5677083333333334</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5677083333333334</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5231788079470199</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8777777777777778</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6556016597510373</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4195804195804196</v>
+      </c>
+      <c r="N29" t="n">
+        <v>79</v>
+      </c>
+      <c r="O29" t="n">
+        <v>11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Video29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>192</v>
+      </c>
+      <c r="C30" t="n">
+        <v>192</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="N30" t="n">
+        <v>90</v>
+      </c>
+      <c r="O30" t="n">
+        <v>9</v>
+      </c>
+      <c r="P30" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Video30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>192</v>
+      </c>
+      <c r="C31" t="n">
+        <v>192</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5886524822695035</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9021739130434783</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7124463519313304</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5562913907284768</v>
+      </c>
+      <c r="N31" t="n">
+        <v>83</v>
+      </c>
+      <c r="O31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P31" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Video31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>192</v>
+      </c>
+      <c r="C32" t="n">
+        <v>192</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5729166666666666</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5729166666666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5309734513274337</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6741573033707865</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.594059405940594</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.6329113924050633</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.4854368932038835</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.5494505494505495</v>
+      </c>
+      <c r="N32" t="n">
+        <v>60</v>
+      </c>
+      <c r="O32" t="n">
+        <v>29</v>
+      </c>
+      <c r="P32" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Video32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>192</v>
+      </c>
+      <c r="C33" t="n">
+        <v>192</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.7760416666666666</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.7760416666666666</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.770053475935829</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.7817258883248731</v>
+      </c>
+      <c r="N33" t="n">
+        <v>72</v>
+      </c>
+      <c r="O33" t="n">
+        <v>22</v>
+      </c>
+      <c r="P33" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Video33</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>192</v>
+      </c>
+      <c r="C34" t="n">
+        <v>192</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.7239583333333334</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.7239583333333334</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6639344262295082</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.7534883720930233</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5858585858585859</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.6863905325443788</v>
+      </c>
+      <c r="N34" t="n">
+        <v>81</v>
+      </c>
+      <c r="O34" t="n">
+        <v>12</v>
+      </c>
+      <c r="P34" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Video34</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>192</v>
+      </c>
+      <c r="C35" t="n">
+        <v>192</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5359477124183006</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6693877551020408</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.4172661870503597</v>
+      </c>
+      <c r="N35" t="n">
+        <v>82</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10</v>
+      </c>
+      <c r="P35" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Video35</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>192</v>
+      </c>
+      <c r="C36" t="n">
+        <v>192</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5572916666666666</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.5572916666666666</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.4967320261437909</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6413502109704642</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.7948717948717948</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.287037037037037</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.4217687074829932</v>
+      </c>
+      <c r="N36" t="n">
+        <v>76</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Video36</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>192</v>
+      </c>
+      <c r="C37" t="n">
+        <v>192</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.6268656716417911</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="N37" t="n">
+        <v>75</v>
+      </c>
+      <c r="O37" t="n">
+        <v>25</v>
+      </c>
+      <c r="P37" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Video37</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>192</v>
+      </c>
+      <c r="C38" t="n">
+        <v>192</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5850340136054422</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7020408163265306</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.351063829787234</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.4748201438848921</v>
+      </c>
+      <c r="N38" t="n">
+        <v>86</v>
+      </c>
+      <c r="O38" t="n">
+        <v>12</v>
+      </c>
+      <c r="P38" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Video38</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>192</v>
+      </c>
+      <c r="C39" t="n">
+        <v>192</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5677083333333334</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5677083333333334</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5035971223021583</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6278026905829596</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.484472049689441</v>
+      </c>
+      <c r="N39" t="n">
+        <v>70</v>
+      </c>
+      <c r="O39" t="n">
+        <v>14</v>
+      </c>
+      <c r="P39" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Video39</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>192</v>
+      </c>
+      <c r="C40" t="n">
+        <v>192</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5763888888888888</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8469387755102041</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6859504132231404</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.351063829787234</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.4647887323943662</v>
+      </c>
+      <c r="N40" t="n">
+        <v>83</v>
+      </c>
+      <c r="O40" t="n">
+        <v>15</v>
+      </c>
+      <c r="P40" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Video40</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>192</v>
+      </c>
+      <c r="C41" t="n">
+        <v>192</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6607142857142857</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7047619047619048</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6820276497695852</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.5632183908045977</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5868263473053892</v>
+      </c>
+      <c r="N41" t="n">
+        <v>74</v>
+      </c>
+      <c r="O41" t="n">
+        <v>31</v>
+      </c>
+      <c r="P41" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Video41</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>192</v>
+      </c>
+      <c r="C42" t="n">
+        <v>192</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5590551181102362</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.797752808988764</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6574074074074074</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.7230769230769231</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.4563106796116505</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.5595238095238095</v>
+      </c>
+      <c r="N42" t="n">
+        <v>71</v>
+      </c>
+      <c r="O42" t="n">
+        <v>18</v>
+      </c>
+      <c r="P42" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Video42</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>192</v>
+      </c>
+      <c r="C43" t="n">
+        <v>192</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6122448979591837</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6557377049180328</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.6448598130841121</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.7340425531914894</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.6865671641791045</v>
+      </c>
+      <c r="N43" t="n">
+        <v>60</v>
+      </c>
+      <c r="O43" t="n">
+        <v>38</v>
+      </c>
+      <c r="P43" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Video43</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>192</v>
+      </c>
+      <c r="C44" t="n">
+        <v>192</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6217948717948718</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8738738738738738</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.7265917602996254</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2716049382716049</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.3760683760683761</v>
+      </c>
+      <c r="N44" t="n">
+        <v>97</v>
+      </c>
+      <c r="O44" t="n">
+        <v>14</v>
+      </c>
+      <c r="P44" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Video44</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>192</v>
+      </c>
+      <c r="C45" t="n">
+        <v>192</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5955882352941176</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8526315789473684</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7012987012987013</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.4329896907216495</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="N45" t="n">
+        <v>81</v>
+      </c>
+      <c r="O45" t="n">
+        <v>14</v>
+      </c>
+      <c r="P45" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Video45</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>192</v>
+      </c>
+      <c r="C46" t="n">
+        <v>192</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6114649681528662</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7413127413127413</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.3222222222222222</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.4640000000000001</v>
+      </c>
+      <c r="N46" t="n">
+        <v>96</v>
+      </c>
+      <c r="O46" t="n">
+        <v>6</v>
+      </c>
+      <c r="P46" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Video46</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>192</v>
+      </c>
+      <c r="C47" t="n">
+        <v>192</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6491228070175439</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.7474747474747475</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.6948356807511736</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.6794871794871795</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.5698924731182796</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.6198830409356725</v>
+      </c>
+      <c r="N47" t="n">
+        <v>74</v>
+      </c>
+      <c r="O47" t="n">
+        <v>25</v>
+      </c>
+      <c r="P47" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Video47</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>192</v>
+      </c>
+      <c r="C48" t="n">
+        <v>192</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5403726708074534</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.6850393700787403</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2525252525252525</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="N48" t="n">
+        <v>87</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Video48</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>192</v>
+      </c>
+      <c r="C49" t="n">
+        <v>192</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.6927083333333334</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6927083333333334</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.6372549019607843</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7471264367816092</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6878306878306877</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.6476190476190476</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.6974358974358975</v>
+      </c>
+      <c r="N49" t="n">
+        <v>65</v>
+      </c>
+      <c r="O49" t="n">
+        <v>22</v>
+      </c>
+      <c r="P49" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Video49</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>192</v>
+      </c>
+      <c r="C50" t="n">
+        <v>192</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7159090909090909</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.7023809523809523</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.5673076923076923</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.6276595744680851</v>
+      </c>
+      <c r="N50" t="n">
+        <v>63</v>
+      </c>
+      <c r="O50" t="n">
+        <v>25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Video50</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>192</v>
+      </c>
+      <c r="C51" t="n">
+        <v>192</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.6754385964912282</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.7884615384615384</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.3942307692307692</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="N51" t="n">
+        <v>77</v>
+      </c>
+      <c r="O51" t="n">
+        <v>11</v>
+      </c>
+      <c r="P51" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Video51</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>192</v>
+      </c>
+      <c r="C52" t="n">
+        <v>192</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.5857142857142857</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8817204301075269</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.703862660944206</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7884615384615384</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.4141414141414141</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.5430463576158939</v>
+      </c>
+      <c r="N52" t="n">
+        <v>82</v>
+      </c>
+      <c r="O52" t="n">
+        <v>11</v>
+      </c>
+      <c r="P52" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Video52</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>192</v>
+      </c>
+      <c r="C53" t="n">
+        <v>192</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9157894736842105</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.4020618556701031</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="N53" t="n">
+        <v>87</v>
+      </c>
+      <c r="O53" t="n">
+        <v>8</v>
+      </c>
+      <c r="P53" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Video53</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>192</v>
+      </c>
+      <c r="C54" t="n">
+        <v>192</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6214285714285714</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7280334728033472</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.4301075268817204</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+      <c r="N54" t="n">
+        <v>87</v>
+      </c>
+      <c r="O54" t="n">
+        <v>12</v>
+      </c>
+      <c r="P54" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Video54</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>192</v>
+      </c>
+      <c r="C55" t="n">
+        <v>192</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5611510791366906</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6812227074235807</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.4019607843137255</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.5290322580645161</v>
+      </c>
+      <c r="N55" t="n">
+        <v>78</v>
+      </c>
+      <c r="O55" t="n">
+        <v>12</v>
+      </c>
+      <c r="P55" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Video55</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>192</v>
+      </c>
+      <c r="C56" t="n">
+        <v>192</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.7287449392712552</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.5109489051094891</v>
+      </c>
+      <c r="N56" t="n">
+        <v>90</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Video56</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>192</v>
+      </c>
+      <c r="C57" t="n">
+        <v>192</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5878378378378378</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9157894736842105</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7160493827160492</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.3711340206185567</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.5106382978723404</v>
+      </c>
+      <c r="N57" t="n">
+        <v>87</v>
+      </c>
+      <c r="O57" t="n">
+        <v>8</v>
+      </c>
+      <c r="P57" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Video57</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>192</v>
+      </c>
+      <c r="C58" t="n">
+        <v>192</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.6510416666666666</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7472527472527473</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6699507389162561</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.5643564356435643</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.6298342541436464</v>
+      </c>
+      <c r="N58" t="n">
+        <v>68</v>
+      </c>
+      <c r="O58" t="n">
+        <v>23</v>
+      </c>
+      <c r="P58" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Video58</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>192</v>
+      </c>
+      <c r="C59" t="n">
+        <v>192</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.7135416666666666</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.7135416666666666</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.7417840375586856</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.8656716417910447</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.5576923076923077</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.6783625730994152</v>
+      </c>
+      <c r="N59" t="n">
+        <v>79</v>
+      </c>
+      <c r="O59" t="n">
+        <v>9</v>
+      </c>
+      <c r="P59" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Video59</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>192</v>
+      </c>
+      <c r="C60" t="n">
+        <v>192</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.6690647482014388</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.7439999999999999</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.660377358490566</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.4320987654320987</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.5223880597014925</v>
+      </c>
+      <c r="N60" t="n">
+        <v>93</v>
+      </c>
+      <c r="O60" t="n">
+        <v>18</v>
+      </c>
+      <c r="P60" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Video60</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>192</v>
+      </c>
+      <c r="C61" t="n">
+        <v>192</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.6927083333333334</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.6927083333333334</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7010309278350515</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.6974358974358974</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.6914893617021277</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.6878306878306879</v>
+      </c>
+      <c r="N61" t="n">
+        <v>68</v>
+      </c>
+      <c r="O61" t="n">
+        <v>30</v>
+      </c>
+      <c r="P61" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Video61</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>192</v>
+      </c>
+      <c r="C62" t="n">
+        <v>192</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6575342465753424</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.4186046511627907</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="N62" t="n">
+        <v>96</v>
+      </c>
+      <c r="O62" t="n">
+        <v>10</v>
+      </c>
+      <c r="P62" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Video62</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>192</v>
+      </c>
+      <c r="C63" t="n">
+        <v>192</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.5729166666666666</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5729166666666666</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8522727272727273</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.646551724137931</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.3365384615384616</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.4605263157894737</v>
+      </c>
+      <c r="N63" t="n">
+        <v>75</v>
+      </c>
+      <c r="O63" t="n">
+        <v>13</v>
+      </c>
+      <c r="P63" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Video63</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>192</v>
+      </c>
+      <c r="C64" t="n">
+        <v>192</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.5234899328859061</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.6976744186046512</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.297029702970297</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="N64" t="n">
+        <v>78</v>
+      </c>
+      <c r="O64" t="n">
+        <v>13</v>
+      </c>
+      <c r="P64" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Video64</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>192</v>
+      </c>
+      <c r="C65" t="n">
+        <v>192</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.6614583333333334</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.6293103448275862</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.7684210526315789</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.6919431279620853</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.7105263157894737</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.5567010309278351</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.6242774566473989</v>
+      </c>
+      <c r="N65" t="n">
+        <v>73</v>
+      </c>
+      <c r="O65" t="n">
+        <v>22</v>
+      </c>
+      <c r="P65" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Video65</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>192</v>
+      </c>
+      <c r="C66" t="n">
+        <v>192</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.5251798561151079</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8795180722891566</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.6576576576576576</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.3944954128440367</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.5308641975308642</v>
+      </c>
+      <c r="N66" t="n">
+        <v>73</v>
+      </c>
+      <c r="O66" t="n">
+        <v>10</v>
+      </c>
+      <c r="P66" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Video66</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>192</v>
+      </c>
+      <c r="C67" t="n">
+        <v>192</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.5369127516778524</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.6639004149377593</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.7209302325581395</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.4335664335664335</v>
+      </c>
+      <c r="N67" t="n">
+        <v>80</v>
+      </c>
+      <c r="O67" t="n">
+        <v>12</v>
+      </c>
+      <c r="P67" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Video67</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>192</v>
+      </c>
+      <c r="C68" t="n">
+        <v>192</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.6721311475409836</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.3191489361702128</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="N68" t="n">
+        <v>82</v>
+      </c>
+      <c r="O68" t="n">
+        <v>16</v>
+      </c>
+      <c r="P68" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Video68</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>192</v>
+      </c>
+      <c r="C69" t="n">
+        <v>192</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.6293103448275862</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.776595744680851</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.6952380952380952</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.7236842105263158</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.5612244897959183</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.6321839080459769</v>
+      </c>
+      <c r="N69" t="n">
+        <v>73</v>
+      </c>
+      <c r="O69" t="n">
+        <v>21</v>
+      </c>
+      <c r="P69" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Video69</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>192</v>
+      </c>
+      <c r="C70" t="n">
+        <v>192</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.5436241610738255</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.9759036144578314</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.6982758620689655</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.9534883720930233</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.3761467889908257</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.5394736842105263</v>
+      </c>
+      <c r="N70" t="n">
+        <v>81</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Video70</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>192</v>
+      </c>
+      <c r="C71" t="n">
+        <v>192</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.6559139784946236</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.6321243523316062</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.6282722513089004</v>
+      </c>
+      <c r="N71" t="n">
+        <v>61</v>
+      </c>
+      <c r="O71" t="n">
+        <v>32</v>
+      </c>
+      <c r="P71" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Video71</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>192</v>
+      </c>
+      <c r="C72" t="n">
+        <v>192</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6183206106870229</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.801980198019802</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6982758620689656</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.6721311475409836</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.4505494505494506</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.5394736842105263</v>
+      </c>
+      <c r="N72" t="n">
+        <v>81</v>
+      </c>
+      <c r="O72" t="n">
+        <v>20</v>
+      </c>
+      <c r="P72" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Video72</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>192</v>
+      </c>
+      <c r="C73" t="n">
+        <v>192</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.5961538461538461</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.7126436781609196</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.2758620689655172</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="N73" t="n">
+        <v>93</v>
+      </c>
+      <c r="O73" t="n">
+        <v>12</v>
+      </c>
+      <c r="P73" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Video73</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>192</v>
+      </c>
+      <c r="C74" t="n">
+        <v>192</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.6379310344827586</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.3148148148148148</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="N74" t="n">
+        <v>74</v>
+      </c>
+      <c r="O74" t="n">
+        <v>10</v>
+      </c>
+      <c r="P74" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Video74</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>192</v>
+      </c>
+      <c r="C75" t="n">
+        <v>192</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.5542168674698795</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.9292929292929293</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.6943396226415094</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2043010752688172</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.319327731092437</v>
+      </c>
+      <c r="N75" t="n">
+        <v>92</v>
+      </c>
+      <c r="O75" t="n">
+        <v>7</v>
+      </c>
+      <c r="P75" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Video75</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>192</v>
+      </c>
+      <c r="C76" t="n">
+        <v>192</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.7154471544715447</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.7927927927927928</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8405797101449275</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.6236559139784946</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.7160493827160493</v>
+      </c>
+      <c r="N76" t="n">
+        <v>88</v>
+      </c>
+      <c r="O76" t="n">
+        <v>11</v>
+      </c>
+      <c r="P76" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Video76</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>192</v>
+      </c>
+      <c r="C77" t="n">
+        <v>192</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.9072164948453608</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.7183673469387756</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.5035971223021581</v>
+      </c>
+      <c r="N77" t="n">
+        <v>88</v>
+      </c>
+      <c r="O77" t="n">
+        <v>9</v>
+      </c>
+      <c r="P77" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Video77</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>192</v>
+      </c>
+      <c r="C78" t="n">
+        <v>192</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.6518987341772152</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.9279279279279279</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.7657992565055762</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.3209876543209876</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.4521739130434782</v>
+      </c>
+      <c r="N78" t="n">
+        <v>103</v>
+      </c>
+      <c r="O78" t="n">
+        <v>8</v>
+      </c>
+      <c r="P78" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Video78</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>192</v>
+      </c>
+      <c r="C79" t="n">
+        <v>192</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.6833333333333333</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.3469387755102041</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.4722222222222222</v>
+      </c>
+      <c r="N79" t="n">
+        <v>82</v>
+      </c>
+      <c r="O79" t="n">
+        <v>12</v>
+      </c>
+      <c r="P79" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Video79</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>192</v>
+      </c>
+      <c r="C80" t="n">
+        <v>192</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.591304347826087</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.7816091954022989</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.6732673267326733</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.7532467532467533</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.5523809523809524</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.6373626373626373</v>
+      </c>
+      <c r="N80" t="n">
+        <v>68</v>
+      </c>
+      <c r="O80" t="n">
+        <v>19</v>
+      </c>
+      <c r="P80" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Video80</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>192</v>
+      </c>
+      <c r="C81" t="n">
+        <v>192</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.5608108108108109</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.9021739130434783</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.6916666666666668</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.486111111111111</v>
+      </c>
+      <c r="N81" t="n">
+        <v>83</v>
+      </c>
+      <c r="O81" t="n">
+        <v>9</v>
+      </c>
+      <c r="P81" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Video81</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>192</v>
+      </c>
+      <c r="C82" t="n">
+        <v>192</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.5885416666666666</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.5885416666666666</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.5182481751824818</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.8452380952380952</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.6425339366515838</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.7636363636363637</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.5153374233128835</v>
+      </c>
+      <c r="N82" t="n">
+        <v>71</v>
+      </c>
+      <c r="O82" t="n">
+        <v>13</v>
+      </c>
+      <c r="P82" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Video82</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>192</v>
+      </c>
+      <c r="C83" t="n">
+        <v>192</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.5885416666666666</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.5885416666666666</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.5539568345323741</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.8191489361702128</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.6609442060085837</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.6792452830188679</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.3673469387755102</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.4768211920529801</v>
+      </c>
+      <c r="N83" t="n">
+        <v>77</v>
+      </c>
+      <c r="O83" t="n">
+        <v>17</v>
+      </c>
+      <c r="P83" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Video83</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>192</v>
+      </c>
+      <c r="C84" t="n">
+        <v>192</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.635036496350365</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.8446601941747572</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.7250000000000001</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.7090909090909091</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.4382022471910113</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="N84" t="n">
+        <v>87</v>
+      </c>
+      <c r="O84" t="n">
+        <v>16</v>
+      </c>
+      <c r="P84" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Video84</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>192</v>
+      </c>
+      <c r="C85" t="n">
+        <v>192</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.6148648648648649</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.8504672897196262</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.7137254901960786</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.3294117647058823</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.4341085271317829</v>
+      </c>
+      <c r="N85" t="n">
+        <v>91</v>
+      </c>
+      <c r="O85" t="n">
+        <v>16</v>
+      </c>
+      <c r="P85" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Video85</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>192</v>
+      </c>
+      <c r="C86" t="n">
+        <v>192</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.6275862068965518</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.900990099009901</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.7398373983739838</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.4065934065934066</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.536231884057971</v>
+      </c>
+      <c r="N86" t="n">
+        <v>91</v>
+      </c>
+      <c r="O86" t="n">
+        <v>10</v>
+      </c>
+      <c r="P86" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Video86</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>192</v>
+      </c>
+      <c r="C87" t="n">
+        <v>192</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.865979381443299</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.6885245901639344</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.3368421052631579</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="N87" t="n">
+        <v>84</v>
+      </c>
+      <c r="O87" t="n">
+        <v>13</v>
+      </c>
+      <c r="P87" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Video87</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>192</v>
+      </c>
+      <c r="C88" t="n">
+        <v>192</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.734375</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.734375</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.7722772277227723</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.7536231884057971</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.7325581395348837</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.7118644067796609</v>
+      </c>
+      <c r="N88" t="n">
+        <v>78</v>
+      </c>
+      <c r="O88" t="n">
+        <v>23</v>
+      </c>
+      <c r="P88" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Video88</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>192</v>
+      </c>
+      <c r="C89" t="n">
+        <v>192</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.8349514563106796</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.7413793103448275</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.7301587301587301</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.5168539325842697</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="N89" t="n">
+        <v>86</v>
+      </c>
+      <c r="O89" t="n">
+        <v>17</v>
+      </c>
+      <c r="P89" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Video89</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>192</v>
+      </c>
+      <c r="C90" t="n">
+        <v>192</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.680672268907563</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.7397260273972603</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.7397260273972602</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.5869565217391305</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.6545454545454545</v>
+      </c>
+      <c r="N90" t="n">
+        <v>81</v>
+      </c>
+      <c r="O90" t="n">
+        <v>19</v>
+      </c>
+      <c r="P90" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Video90</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>192</v>
+      </c>
+      <c r="C91" t="n">
+        <v>192</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.6330935251798561</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.8380952380952381</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.7213114754098361</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.6792452830188679</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="N91" t="n">
+        <v>88</v>
+      </c>
+      <c r="O91" t="n">
+        <v>17</v>
+      </c>
+      <c r="P91" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Video91</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>192</v>
+      </c>
+      <c r="C92" t="n">
+        <v>192</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.734375</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.734375</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.7310924369747899</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.8207547169811321</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.7397260273972602</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.6279069767441861</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.6792452830188678</v>
+      </c>
+      <c r="N92" t="n">
+        <v>87</v>
+      </c>
+      <c r="O92" t="n">
+        <v>19</v>
+      </c>
+      <c r="P92" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Video92</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>192</v>
+      </c>
+      <c r="C93" t="n">
+        <v>192</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.6330935251798561</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.8543689320388349</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.7169811320754716</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.4269662921348314</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.5352112676056338</v>
+      </c>
+      <c r="N93" t="n">
+        <v>88</v>
+      </c>
+      <c r="O93" t="n">
+        <v>15</v>
+      </c>
+      <c r="P93" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Video93</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>192</v>
+      </c>
+      <c r="C94" t="n">
+        <v>192</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.671875</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.6453900709219859</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.7450980392156863</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.5467625899280576</v>
+      </c>
+      <c r="N94" t="n">
+        <v>91</v>
+      </c>
+      <c r="O94" t="n">
+        <v>13</v>
+      </c>
+      <c r="P94" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Video94</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>192</v>
+      </c>
+      <c r="C95" t="n">
+        <v>192</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.652542372881356</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.8020833333333334</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.719626168224299</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.7432432432432432</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.5729166666666666</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="N95" t="n">
+        <v>77</v>
+      </c>
+      <c r="O95" t="n">
+        <v>19</v>
+      </c>
+      <c r="P95" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Video95</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>192</v>
+      </c>
+      <c r="C96" t="n">
+        <v>192</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.5774647887323944</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.6949152542372881</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.3877551020408163</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.5135135135135135</v>
+      </c>
+      <c r="N96" t="n">
+        <v>82</v>
+      </c>
+      <c r="O96" t="n">
+        <v>12</v>
+      </c>
+      <c r="P96" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Video96</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>192</v>
+      </c>
+      <c r="C97" t="n">
+        <v>192</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.6302083333333334</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.8829787234042553</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.7004219409282701</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.3877551020408163</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.5170068027210885</v>
+      </c>
+      <c r="N97" t="n">
+        <v>83</v>
+      </c>
+      <c r="O97" t="n">
+        <v>11</v>
+      </c>
+      <c r="P97" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Video97</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>192</v>
+      </c>
+      <c r="C98" t="n">
+        <v>192</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.5496688741721855</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.9222222222222223</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.6887966804979253</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.8292682926829268</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.4755244755244755</v>
+      </c>
+      <c r="N98" t="n">
+        <v>83</v>
+      </c>
+      <c r="O98" t="n">
+        <v>7</v>
+      </c>
+      <c r="P98" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Video98</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>192</v>
+      </c>
+      <c r="C99" t="n">
+        <v>192</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.640625</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.6126760563380281</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.8613861386138614</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.7160493827160493</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.3956043956043956</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.5106382978723404</v>
+      </c>
+      <c r="N99" t="n">
+        <v>87</v>
+      </c>
+      <c r="O99" t="n">
+        <v>14</v>
+      </c>
+      <c r="P99" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Video99</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>192</v>
+      </c>
+      <c r="C100" t="n">
+        <v>192</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.5584415584415584</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.7049180327868853</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="N100" t="n">
+        <v>86</v>
+      </c>
+      <c r="O100" t="n">
+        <v>4</v>
+      </c>
+      <c r="P100" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Video100</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>192</v>
+      </c>
+      <c r="C101" t="n">
+        <v>192</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.5785714285714286</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.826530612244898</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.680672268907563</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.6730769230769231</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.3723404255319149</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.4794520547945206</v>
+      </c>
+      <c r="N101" t="n">
+        <v>81</v>
+      </c>
+      <c r="O101" t="n">
+        <v>17</v>
+      </c>
+      <c r="P101" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1409,10 +7011,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8038</v>
+        <v>8039</v>
       </c>
       <c r="C2" t="n">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="3">
@@ -1422,10 +7024,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5403</v>
+        <v>5400</v>
       </c>
       <c r="C3" t="n">
-        <v>4243</v>
+        <v>4246</v>
       </c>
     </row>
   </sheetData>
